--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,10 +441,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Prompt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Prompt Image Ingredients</t>
         </is>
@@ -453,46 +458,139 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Creamy Garlic Spinach Pasta 🍝🌿
+          <t>Pizza Party Delight 🍕🎉
 Ingredients:
-- 8 oz fettuccine pasta
-- 2 cups fresh spinach
-- 3 cloves garlic, minced
-- 1 cup heavy cream
-- 1/2 cup grated Parmesan cheese
-- 2 tbsp olive oil
-- Salt and pepper to taste
-- Red pepper flakes (optional)
+- 2 cups all-purpose flour
+- 1 cup pizza sauce
+- 1 ½ cups shredded mozzarella cheese
+- 1 cup pepperoni slices
+- 1 tablespoon olive oil
+- 1 teaspoon dried oregano
+- 1 teaspoon garlic powder
+- ½ teaspoon salt
+- ½ teaspoon sugar
+- ¾ cup warm water (about 110°F)
 Instructions:
-1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
-2. In a large skillet, heat the olive oil over medium heat. Add the minced garlic and sauté for about 1 minute until fragrant.
-3. Add the fresh spinach to the skillet and cook until wilted, about 2-3 minutes.
-4. Pour in the heavy cream and bring to a gentle simmer. Stir well to combine.
-5. Add the grated Parmesan cheese and mix until melted and creamy. Season with salt, pepper, and red pepper flakes if using.
-6. Toss the cooked fettuccine in the creamy spinach sauce until well coated.
-7. Serve immediately, garnished with extra Parmesan cheese if desired.
-Prep Time: 10 minutes
+1. In a large mixing bowl, combine the flour, salt, sugar, garlic powder, and oregano.
+2. Gradually add warm water and olive oil to the dry ingredients, mixing until a dough forms.
+3. Knead the dough on a floured surface for about 5 minutes until smooth and elastic.
+4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm area for 1 hour or until doubled in size.
+5. Preheat your oven to 475°F (245°C).
+6. Roll out the risen dough on a floured surface to your desired thickness and shape.
+7. Transfer the dough to a pizza stone or baking sheet and spread pizza sauce evenly over the surface.
+8. Sprinkle mozzarella cheese generously on top, followed by the pepperoni slices.
+9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
+10. Remove the pizza from the oven, let it cool for a few minutes, then slice and serve.
+Prep Time: 15 minutes
 Cook Time: 15 minutes
-Total Time: 25 minutes
+Total Time: 1 hour 30 minutes
 Course: Main Course
 Cuisine: Italian
 Servings: 4
-Calories: ~450 per serving</t>
+Calories: ~400 per serving</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Realistic, appetizing ULTRA close-up of creamy garlic spinach pasta served in a clean white ceramic bowl, on a light neutral surface. The dish features fettuccine coated in a rich cream sauce with vibrant green spinach, garnished with grated Parmesan cheese and a sprinkle of red pepper flakes. The composition fills 90–100% of the frame, showcasing the texture of the pasta and sauce, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the food, captured from a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+          <t>{
+  "name": "pizza",
+  "summary": "This delicious pizza is topped with mozzarella cheese and pepperoni, perfect for a pizza party. Easy to make with a homemade dough.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "15",
+  "total_time": "90",
+  "calories": "400",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pizza",
+    "cheese",
+    "pepperoni",
+    "dough",
+    "Italian",
+    "main course"
+  ],
+  "notes": "Let the dough rise in a warm area for best results. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "pizza sauce"
+    },
+    {
+      "amount": "1 ½",
+      "unit": "cups",
+      "name": "shredded mozzarella cheese"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "pepperoni slices"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "dried oregano"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "½",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "½",
+      "unit": "teaspoon",
+      "name": "sugar"
+    },
+    {
+      "amount": "¾",
+      "unit": "cup",
+      "name": "warm water"
+    }
+  ],
+  "instructions": [
+    "In a large mixing bowl, combine the flour, salt, sugar, garlic powder, and oregano.",
+    "Gradually add warm water and olive oil to the dry ingredients, mixing until a dough forms.",
+    "Knead the dough on a floured surface for about 5 minutes until smooth and elastic.",
+    "Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm area for 60 minutes or until doubled in size.",
+    "Preheat your oven to 475°F (245°C).",
+    "Roll out the risen dough on a floured surface to your desired thickness and shape.",
+    "Transfer the dough to a pizza stone or baking sheet and spread pizza sauce evenly over the surface.",
+    "Sprinkle mozzarella cheese generously on top, followed by the pepperoni slices.",
+    "Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.",
+    "Remove the pizza from the oven, let it cool for a few minutes, then slice and serve."
+  ]
+}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fettuccine pasta, spinach, garlic, heavy cream, Parmesan cheese, olive oil, salt, pepper, red pepper flakes, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+          <t>Realistic, appetizing ULTRA close-up of a freshly baked pepperoni pizza topped with melted mozzarella cheese, served on a clean white ceramic plate. The pizza features a golden crust, vibrant red pizza sauce peeking out from under the cheese, and perfectly arranged pepperoni slices. The composition fills 90–100% of the frame, showcasing the texture of the cheese and the crust, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the pizza, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>flour, pizza sauce, mozzarella cheese, pepperoni, olive oil, oregano, garlic powder, salt, sugar, water, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,21 +439,6 @@
           <t>Recipe</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Json Recipe</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt Image Ingredients</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,134 +448,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pizza Party Delight 🍕🎉
+          <t>Pizza Delight 🍕✨
 Ingredients:
 - 2 cups all-purpose flour
+- 1 packet (2 1/4 tsp) active dry yeast
+- 1 teaspoon sugar
+- 3/4 cup warm water
+- 1 tablespoon olive oil
+- 1 teaspoon salt
 - 1 cup pizza sauce
-- 1 ½ cups shredded mozzarella cheese
-- 1 cup pepperoni slices
-- 1 tablespoon olive oil
-- 1 teaspoon dried oregano
-- 1 teaspoon garlic powder
-- ½ teaspoon salt
-- ½ teaspoon sugar
-- ¾ cup warm water (about 110°F)
+- 2 cups shredded mozzarella cheese
+- 1/2 cup sliced pepperoni
+- 1/4 cup grated Parmesan cheese
+- Fresh basil leaves for garnish
 Instructions:
-1. In a large mixing bowl, combine the flour, salt, sugar, garlic powder, and oregano.
-2. Gradually add warm water and olive oil to the dry ingredients, mixing until a dough forms.
-3. Knead the dough on a floured surface for about 5 minutes until smooth and elastic.
-4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm area for 1 hour or until doubled in size.
+1. In a small bowl, combine warm water, sugar, and yeast. Let it sit for about 5 minutes until foamy.
+2. In a large mixing bowl, combine flour and salt. Make a well in the center and add the yeast mixture and olive oil.
+3. Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.
+4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for 1 hour or until doubled in size.
 5. Preheat your oven to 475°F (245°C).
-6. Roll out the risen dough on a floured surface to your desired thickness and shape.
-7. Transfer the dough to a pizza stone or baking sheet and spread pizza sauce evenly over the surface.
-8. Sprinkle mozzarella cheese generously on top, followed by the pepperoni slices.
-9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
-10. Remove the pizza from the oven, let it cool for a few minutes, then slice and serve.
+6. Roll out the dough on a floured surface to your desired thickness and transfer to a pizza stone or baking sheet.
+7. Spread the pizza sauce evenly over the dough, leaving a small border around the edges.
+8. Sprinkle mozzarella cheese over the sauce, followed by the pepperoni and Parmesan cheese.
+9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and cheese is bubbly.
+10. Remove from the oven and garnish with fresh basil leaves before slicing.
+11. Serve hot and enjoy your delicious homemade pizza!
 Prep Time: 15 minutes
 Cook Time: 15 minutes
 Total Time: 1 hour 30 minutes
 Course: Main Course
 Cuisine: Italian
 Servings: 4
-Calories: ~400 per serving</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{
-  "name": "pizza",
-  "summary": "This delicious pizza is topped with mozzarella cheese and pepperoni, perfect for a pizza party. Easy to make with a homemade dough.",
-  "servings": "4",
-  "prep_time": "15",
-  "cook_time": "15",
-  "total_time": "90",
-  "calories": "400",
-  "course": "Main Course",
-  "cuisine": "Italian",
-  "keywords": [
-    "pizza",
-    "cheese",
-    "pepperoni",
-    "dough",
-    "Italian",
-    "main course"
-  ],
-  "notes": "Let the dough rise in a warm area for best results. Calories are per serving.",
-  "ingredients": [
-    {
-      "amount": "2",
-      "unit": "cups",
-      "name": "all-purpose flour"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "pizza sauce"
-    },
-    {
-      "amount": "1 ½",
-      "unit": "cups",
-      "name": "shredded mozzarella cheese"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "pepperoni slices"
-    },
-    {
-      "amount": "1",
-      "unit": "tablespoon",
-      "name": "olive oil"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "dried oregano"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "garlic powder"
-    },
-    {
-      "amount": "½",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "½",
-      "unit": "teaspoon",
-      "name": "sugar"
-    },
-    {
-      "amount": "¾",
-      "unit": "cup",
-      "name": "warm water"
-    }
-  ],
-  "instructions": [
-    "In a large mixing bowl, combine the flour, salt, sugar, garlic powder, and oregano.",
-    "Gradually add warm water and olive oil to the dry ingredients, mixing until a dough forms.",
-    "Knead the dough on a floured surface for about 5 minutes until smooth and elastic.",
-    "Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm area for 60 minutes or until doubled in size.",
-    "Preheat your oven to 475°F (245°C).",
-    "Roll out the risen dough on a floured surface to your desired thickness and shape.",
-    "Transfer the dough to a pizza stone or baking sheet and spread pizza sauce evenly over the surface.",
-    "Sprinkle mozzarella cheese generously on top, followed by the pepperoni slices.",
-    "Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.",
-    "Remove the pizza from the oven, let it cool for a few minutes, then slice and serve."
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a freshly baked pepperoni pizza topped with melted mozzarella cheese, served on a clean white ceramic plate. The pizza features a golden crust, vibrant red pizza sauce peeking out from under the cheese, and perfectly arranged pepperoni slices. The composition fills 90–100% of the frame, showcasing the texture of the cheese and the crust, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the pizza, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>flour, pizza sauce, mozzarella cheese, pepperoni, olive oil, oregano, garlic powder, salt, sugar, water, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+Calories: ~350 per serving</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,47 +439,14 @@
           <t>Recipe</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>Generated At</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pizza Delight 🍕✨
-Ingredients:
-- 2 cups all-purpose flour
-- 1 packet (2 1/4 tsp) active dry yeast
-- 1 teaspoon sugar
-- 3/4 cup warm water
-- 1 tablespoon olive oil
-- 1 teaspoon salt
-- 1 cup pizza sauce
-- 2 cups shredded mozzarella cheese
-- 1/2 cup sliced pepperoni
-- 1/4 cup grated Parmesan cheese
-- Fresh basil leaves for garnish
-Instructions:
-1. In a small bowl, combine warm water, sugar, and yeast. Let it sit for about 5 minutes until foamy.
-2. In a large mixing bowl, combine flour and salt. Make a well in the center and add the yeast mixture and olive oil.
-3. Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.
-4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for 1 hour or until doubled in size.
-5. Preheat your oven to 475°F (245°C).
-6. Roll out the dough on a floured surface to your desired thickness and transfer to a pizza stone or baking sheet.
-7. Spread the pizza sauce evenly over the dough, leaving a small border around the edges.
-8. Sprinkle mozzarella cheese over the sauce, followed by the pepperoni and Parmesan cheese.
-9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and cheese is bubbly.
-10. Remove from the oven and garnish with fresh basil leaves before slicing.
-11. Serve hot and enjoy your delicious homemade pizza!
-Prep Time: 15 minutes
-Cook Time: 15 minutes
-Total Time: 1 hour 30 minutes
-Course: Main Course
-Cuisine: Italian
-Servings: 4
-Calories: ~350 per serving</t>
+          <t>Json Recipe</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,1258 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Image Ingredients</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>main_image</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>image_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>image_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>image_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>image_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>statu</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>main_image_ingredients</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>statu_ing</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>error_ing</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statut Article</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_article</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_title_pin</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_keywords</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_focus_keyword</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_pillar_content</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_image</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Bowl You’ll Love</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Bowl You’ll Love 🍗🥗
+Ingredients:
+- 1 cup cooked quinoa
+- 1 lb grilled chicken breast, diced
+- 1 cup black beans, rinsed and drained
+- 1 cup cherry tomatoes, halved
+- 1 avocado, sliced
+- 1 cup corn (fresh or frozen)
+- 1/4 cup Greek yogurt
+- 1 tbsp lime juice
+- Salt and pepper to taste
+- Fresh cilantro for garnish
+Instructions:
+1. In a large bowl, combine the cooked quinoa, black beans, corn, and cherry tomatoes.
+2. Add the diced grilled chicken to the bowl and mix well.
+3. In a small bowl, whisk together Greek yogurt, lime juice, salt, and pepper until smooth.
+4. Drizzle the yogurt dressing over the chicken and quinoa mixture.
+5. Gently toss everything together until evenly coated.
+6. Top the bowl with avocado slices and garnish with fresh cilantro.
+7. Serve immediately and enjoy your high-protein chicken bowl!
+Prep Time: 15 minutes
+Cook Time: 15 minutes
+Total Time: 30 minutes
+Course: Main Course
+Cuisine: American
+Servings: 4
+Calories: ~450 per serving</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:52:42</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Easy High Protein Chicken Bowl",
+  "summary": "This Easy High Protein Chicken Bowl is a delicious and nutritious meal packed with flavor and protein. Perfect for a quick lunch or dinner.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "15",
+  "total_time": "30",
+  "calories": "450",
+  "course": "Main Course",
+  "cuisine": "American",
+  "keywords": [
+    "chicken",
+    "quinoa",
+    "high protein",
+    "healthy",
+    "bowl",
+    "easy",
+    "meal prep"
+  ],
+  "notes": "Feel free to customize with your favorite vegetables. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "cooked quinoa"
+    },
+    {
+      "amount": "1",
+      "unit": "lb",
+      "name": "grilled chicken breast, diced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "black beans, rinsed and drained"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "cherry tomatoes, halved"
+    },
+    {
+      "amount": "1",
+      "unit": "",
+      "name": "avocado, sliced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "corn (fresh or frozen)"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "Greek yogurt"
+    },
+    {
+      "amount": "1",
+      "unit": "tbsp",
+      "name": "lime juice"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh cilantro for garnish"
+    }
+  ],
+  "instructions": [
+    "In a large bowl, combine the cooked quinoa, black beans, corn, and cherry tomatoes.",
+    "Add the diced grilled chicken to the bowl and mix well.",
+    "In a small bowl, whisk together Greek yogurt, lime juice, salt, and pepper until smooth.",
+    "Drizzle the yogurt dressing over the chicken and quinoa mixture.",
+    "Gently toss everything together until evenly coated.",
+    "Top the bowl with avocado slices and garnish with fresh cilantro.",
+    "Serve immediately and enjoy your high-protein chicken bowl!"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a high protein chicken bowl featuring cooked quinoa, diced grilled chicken breast, black beans, cherry tomatoes, sliced avocado, and corn, all beautifully arranged in a clean white ceramic bowl. The dish is drizzled with a creamy Greek yogurt dressing and garnished with fresh cilantro. The composition fills 90–100% of the frame, showcasing clear food texture with a shallow depth of field and soft natural daylight casting gentle shadows. The focus is sharp at the center of the food, presented at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>quinoa, chicken, black beans, cherry tomatoes, avocado, corn, Greek yogurt, lime juice, cilantro, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521000/9bdd9beae68.png</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521000/d950351edcc.png</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521000/29630db59b7.png</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521000/a80696ec7f8.png</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521000/1dc851246ac.png</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521001/65d82945daa.png</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/d3f028278cc.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/cec4708c29a.png</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/a796f37517d.png</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/9c7aba3de92.png</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy High Protein Chicken Bowl
+## Introduction
+Exploring nutritious meals that maintain a balance of flavor and health is essential in today’s fast-paced world. This Easy High Protein Chicken Bowl is not only simple to prepare but also filled with vibrant ingredients that offer a myriad of health benefits. Packed with protein, fiber, and essential vitamins, this dish is perfect for a nourishing lunch or dinner. 
+With the combination of grilled chicken breast, quinoa, and a colorful medley of vegetables, the Easy High Protein Chicken Bowl offers not just flavor, but also the ideal nutrients your body needs to recover and thrive. Whether you’re looking for a healthy meal to fuel your workouts or simply aiming to prepare a delightful dinner for your family, this bowl can do it all.
+The beauty of this dish lies in its versatility. You can easily customize it based on seasonal ingredients or your personal preferences. The high content of protein and fiber will keep you satisfied without feeling weighed down, making this bowl an excellent option for busy weekdays or leisurely weekend lunches. Easy to whip up and even easier to enjoy, the Easy High Protein Chicken Bowl is a recipe you'll want to keep in your kitchen repertoire.
+## Recipe Overview
+- Prep Time: 15 minutes  
+- Cook Time: 15 minutes  
+- Total Time: 30 minutes  
+- Course: Main Course  
+- Cuisine: American  
+- Servings: 4  
+- Calories: ~450 per serving  
+## Ingredients
+- 1 cup cooked quinoa  
+- 1 lb grilled chicken breast, diced  
+- 1 cup black beans, rinsed and drained  
+- 1 cup cherry tomatoes, halved  
+- 1 avocado, sliced  
+- 1 cup corn (fresh or frozen)  
+- 1/4 cup Greek yogurt  
+- 1 tbsp lime juice  
+- Salt and pepper to taste  
+- Fresh cilantro for garnish
+{{image_ing_1}}
+## Instructions
+1. In a large bowl, combine the cooked quinoa, black beans, corn, and cherry tomatoes.
+2. Add the diced grilled chicken to the bowl and mix well.
+3. In a small bowl, whisk together Greek yogurt, lime juice, salt, and pepper until smooth.
+4. Drizzle the yogurt dressing over the chicken and quinoa mixture.
+5. Gently toss everything together until evenly coated.
+6. Top the bowl with avocado slices and garnish with fresh cilantro.
+7. Serve immediately and enjoy your high-protein chicken bowl!
+Exploring the essential components of this Quick High Protein Chicken Bowl reveals not only the richness of flavors, but also the wholesome nutrition each ingredient brings to the table.
+This dish begins with **cooked quinoa**, a gluten-free grain renowned for its high protein content and complete amino acid profile. Quinoa is also rich in magnesium, iron, and vitamin B6, making it an excellent base for our bowl. From its nutty flavor to its light, fluffy texture, it complements the other ingredients wonderfully. When preparing quinoa, it's important to rinse it thoroughly before cooking to remove any bitterness, ensuring a pleasant taste in your dish.
+Next, we have **grilled chicken breast**, a lean source of protein that supports muscle recovery and growth. Grilled chicken adds a smoky flavor and juicy bite to the bowl, enhancing the overall experience. The key to perfectly grilled chicken is ensuring it is marinated well and cooked to the ideal temperature to keep it tender. Dicing it before adding to the bowl allows for better distribution of flavors, making every bite a delightful mix of ingredients.
+Then there are **black beans**, which provide a substantial amount of dietary fiber, protein, and antioxidants. They are not only beneficial for digestion but also help in maintaining a healthy heart. When using canned black beans, it is crucial to rinse and drain them properly to eliminate excess sodium. If you'd like to try different flavors, you could substitute the black beans with other legumes such as kidney beans or chickpeas for some variety.
+Adding **cherry tomatoes** brings a burst of color and sweetness to the bowl. Their juicy texture complements the other ingredients beautifully. When selecting cherry tomatoes, opt for the ripe ones that feel slightly firm to the touch. They should be stored at room temperature and consumed within a week to ensure freshness.
+Next up is the **avocado**, which not only lends creaminess and richness to the dish but is also packed with healthy fats, vitamins, and minerals. When preparing avocado, look for ones that yield slightly to gentle pressure, indicating ripeness. Slicing it just before serving prevents it from browning too quickly, preserving its fresh flavor and vibrant color.
+The dish wouldn’t be complete without **corn**, which can be either fresh or frozen, depending on your preference and availability. Corn is high in fiber and essential nutrients, providing a natural sweetness that balances the other flavors in the bowl. If using fresh corn, consider lightly grilling or steaming it to enhance its sweetness. Frozen corn is also a great option as it retains its nutrients well, making it a convenient choice.
+A standout feature of this chicken bowl is the incorporation of **Greek yogurt**, which serves as a creamy dressing. It is richer in protein than regular yogurt and contains probiotics, promoting gut health. You can easily whip it into a dressing by adding lime juice, salt, and pepper, creating a refreshing sauce that ties all the components together.
+Lastly, the addition of **lime juice** elevates the flavors by adding brightness and tang. Freshly squeezed lime juice enhances the taste of all the ingredients, ensuring a well-rounded flavor profile. If you do not have any lime on hand, vinegar or lemon juice can serve as suitable substitutes.
+This Easy High Protein Chicken Bowl not only satiates, but it also combines unique textures and flavors from fresh, wholesome ingredients. Staying committed to the principles of healthy eating doesn’t mean sacrificing on flavor. With this recipe, you can delight in both nutrition and taste, making it a staple in your meal-prep itinerary.
+### Seasoning
+Seasoning plays a vital role in elevating the flavors of any dish, and the Easy High Protein Chicken Bowl is no exception. Salt and pepper are the foundational seasonings that create a balanced flavor profile, enhancing the natural tastes of each ingredient. The right amount of salt can bring out the sweetness of the cherry tomatoes, while pepper adds depth to the overall flavor.
+To take your chicken bowl to the next level, consider incorporating additional seasonings. Spices like cumin or smoked paprika can add warmth, while garlic powder or onion powder can infuse a savory aroma. You might also explore using a sprinkle of cayenne pepper for a touch of heat or a dash of chili powder for depth. Always taste as you go, and remember that seasoning should enhance, not overpower, the main components of the dish.
+Techniques for seasoning properly start with seasoning the quinoa while it cooks, allowing flavors to absorb into the grains. When mixing your ingredients, adding salt and pepper at each stage rather than just at the end can result in a well-rounded and flavorful chicken bowl.
+### Fresh Cilantro
+Cilantro is not merely a garnish; it plays a crucial role in refreshing the dish. Its crisp, slightly citrusy flavor harmonizes beautifully with the rich avocado and grilled chicken. Additionally, cilantro is packed with health benefits, including antioxidants and anti-inflammatory properties, making it a nutritious addition to any meal.
+Proper handling of cilantro ensures it stays fresh longer. When purchasing, select cilantro with vibrant green leaves and avoid any that appear wilted. Once home, wash the cilantro thoroughly to remove any dirt or chemicals, then store it in a glass of water in the refrigerator or wrapped in a damp cloth for optimal freshness. If you want to get creative, cilantro can be used in salsas, salads, and sauces or as a flavor enhancer in stir-fries and soups.
+## Preparation Steps
+Achieving the best flavor and texture in your chicken bowl involves several important preparation steps. Start by cooking the quinoa according to package instructions, ensuring it’s fluffy and well-seasoned. While the quinoa cooks, grill the chicken breast and cut it into even, bite-sized pieces to guarantee consistent cooking.
+Next, rinse and drain the black beans to remove excess sodium and any canned residue. Halve the cherry tomatoes, which will provide bursts of juiciness in each bite. If using frozen corn, ensure it’s thawed or warmed for a tender texture. Each step contributes to the final dish's flavor and texture; for example, ensuring that the quinoa is cool before mixing prevents the avocado from turning brown too quickly.
+Common mistakes to avoid during preparation include overcooking the quinoa, which can lead to mushiness, as well as mixing ingredients too vigorously, potentially damaging the delicate avocado slices. Careful preparation ensures that every component shines in the bowl.
+### Combining Ingredients
+The interaction of ingredients when combined is crucial for flavor development in your chicken bowl. When you combine cooked quinoa, black beans, corn, and cherry tomatoes, the moisture from the tomatoes and corn can help each grain of quinoa clump lightly and absorb flavors effectively. Adding the grilled chicken later allows for a gentle mix without losing its texture.
+Thorough mixing is essential as well. This ensures that the yogurt dressing coats every ingredient uniformly, enhancing the overall experience. It’s advisable to use gentle folding motions rather than vigorous stirring, preserving the integrity of the avocado slices.
+### Making the Yogurt Dressing
+Creating the yogurt dressing is simple but pivotal for tying the dish together. Start by adding Greek yogurt to a bowl, followed by freshly squeezed lime juice, salt, and pepper. Whisking these ingredients creates a creamy dressing that complements the protein-rich chicken and balances the sweetness of the corn and tomatoes.
+For a smooth texture in the dressing, use room temperature yogurt. If you find your dressing too thick, consider adding a splash of water or additional lime juice to reach your desired consistency. If you wish to change the flavor profile, explore adding herbs like dill or parsley for freshness, or a hint of honey for sweetness.
+### Assembly of the Bowl
+The visual appeal of a dish often enhances the dining experience, especially with the Easy High Protein Chicken Bowl. When assembling, begin with a base layer of quinoa, followed by the black beans and corn for a colorful mix. Next, carefully arrange the diced grilled chicken evenly throughout the bowl. Finally, tuck in sliced avocado artistically on top.
+For added garnishing ideas, consider using crumbled feta cheese, chopped green onions, or sliced radishes to add a pop of color and flavor. Serving the bowl immediately after assembly ensures that the freshness of the ingredients, especially the avocado and herbs, is preserved.
+## Serving Suggestions
+While the chicken bowl is a satisfying main course on its own, consider pairing it with side dishes for an elaborate meal. Serving alongside a refreshing cucumber salad or a light fruit platter can offer additional textures and flavors. For those with dietary needs, this bowl can easily be customized; replacing chicken with tofu or tempeh creates a delightful vegan option.
+To cater to children or picky eaters, consider deconstructing the bowl into individual components. Allowing them to create their own assembly can invite them to partake in enjoying the meal more fully.
+## Nutritional Information
+With an approximate calorie count of ~450 per serving, the Easy High Protein Chicken Bowl is a nutritionally balanced meal option. Each bowl delivers essential nutrients, providing a good source of protein from the chicken and beans, healthy fats from the avocado, and fiber from the quinoa and vegetables. The inclusion of Greek yogurt not only adds creaminess but also boosts the protein content.
+This balanced meal is an excellent way to incorporate a variety of food groups, ensuring you are consuming necessary vitamins and minerals while enjoying your meal.
+## Variations and Modifications
+If you're looking to adapt this recipe to fit specific dietary needs, consider vegetarian or vegan adaptations. Replace the grilled chicken with chickpeas or black beans for a protein-packed alternative. You can also add various vegetables, such as roasted bell peppers, sweet potatoes, or zucchini, to increase nutritional density and visual appeal.
+Additionally, explore flavor variations by using different condiments or sauces. A dollop of spicy salsa, a splash of BBQ sauce, or a drizzle of tahini can transform the dish while still keeping the original framework intact.
+## Meal Prep Tips
+For those looking to prepare the Easy High Protein Chicken Bowl ahead of time, consider cooking and storing each component separately. Cooked quinoa, grilled chicken, and vegetables can all be refrigerated and assembled as needed, keeping ingredients fresh. The yogurt dressing can also be made in advance and stored in an airtight container.
+When reheating leftovers, do so gently to avoid overcooking the ingredients. Storing ingredients properly can enhance their longevity; for instance, keeping avocados aside from the rest until ready to eat prevents browning.
+## Conclusion
+This Easy High Protein Chicken Bowl is a delightful blend of flavors and textures that come together in just 30 minutes. With a protein-packed profile and generous servings, it is a satisfying meal that doesn’t compromise on taste or health. Enjoy the vibrant ingredients and creamy dressing as a quick weeknight dinner or a filling lunch!
+</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Healthy High Protein Chicken Bowl Recipe with Quinoa, Beans, and Avocado</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>High-Protein Chicken Quinoa Bowl</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>This healthy high protein chicken bowl recipe is perfect for a nutritious and satisfying meal any time of year. Packed with quinoa, black beans, creamy avocado, and a dollop of Greek yogurt, it's a wholesome dish that balances flavors and textures beautifully. Enjoy this vibrant bowl as a refreshing option for lunch or dinner that supports a healthy lifestyle.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>high protein, chicken bowl, quinoa, black beans, avocado, Greek yogurt</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Enjoy a delicious Easy High Protein Chicken Bowl packed with nutritious ingredients for a satisfying meal in just 30 minutes!</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A1-Pinterest_01-out/output_images/image_1.jpg</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-high-protein-chicken-bowl-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl Better Than Takeout</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl Better Than Takeout 🍲🥗
+Ingredients:
+- 1 lb boneless, skinless chicken breast, diced
+- 2 cups cooked quinoa
+- 1 cup broccoli florets
+- 1 red bell pepper, diced
+- 1 avocado, sliced
+- 2 tablespoons olive oil
+- 2 tablespoons soy sauce (low sodium)
+- 1 tablespoon honey
+- 1 teaspoon garlic powder
+- Salt and pepper to taste
+- Fresh cilantro for garnish
+Instructions:
+1. In a large bowl, combine olive oil, soy sauce, honey, garlic powder, salt, and pepper. Mix well to create a marinade.
+2. Add the diced chicken to the marinade and let it sit for at least 15 minutes.
+3. While the chicken marinates, steam the broccoli florets until they are tender, about 5-7 minutes.
+4. In a large skillet over medium heat, add the marinated chicken and cook for 6-8 minutes, or until fully cooked and golden brown.
+5. In serving bowls, layer the cooked quinoa, followed by the sautéed chicken, steamed broccoli, and diced red bell pepper.
+6. Top each bowl with sliced avocado and fresh cilantro for garnish.
+7. Drizzle any remaining marinade over the bowls for added flavor.
+8. Serve immediately and enjoy your healthy chicken bowl!
+Prep Time: 15 minutes
+Cook Time: 15 minutes
+Total Time: 30 minutes
+Course: Main Course
+Cuisine: Healthy
+Servings: 4
+Calories: ~450 per serving</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:52:56</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Healthy Chicken Bowl Better Than Takeout",
+  "summary": "This healthy chicken bowl is a nutritious and delicious alternative to takeout, featuring marinated chicken, quinoa, and fresh vegetables. It's quick to prepare and packed with flavor.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "15",
+  "total_time": "30",
+  "calories": "450",
+  "course": "Main Course",
+  "cuisine": "Healthy",
+  "keywords": [
+    "chicken",
+    "quinoa",
+    "healthy",
+    "bowl",
+    "easy",
+    "dinner"
+  ],
+  "notes": "Feel free to customize with your favorite vegetables. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "lb",
+      "name": "boneless, skinless chicken breast, diced"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "cooked quinoa"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "broccoli florets"
+    },
+    {
+      "amount": "1",
+      "unit": "",
+      "name": "red bell pepper, diced"
+    },
+    {
+      "amount": "1",
+      "unit": "",
+      "name": "avocado, sliced"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "olive oil"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "soy sauce (low sodium)"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "honey"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh cilantro for garnish"
+    }
+  ],
+  "instructions": [
+    "In a large bowl, combine olive oil, soy sauce, honey, garlic powder, salt, and pepper to create a marinade.",
+    "Add the diced chicken to the marinade and let it sit for at least 15 minutes.",
+    "Steam the broccoli florets until tender, about 5-7 minutes.",
+    "In a large skillet over medium heat, add the marinated chicken and cook for 6-8 minutes until fully cooked and golden brown.",
+    "In serving bowls, layer the cooked quinoa, sautéed chicken, steamed broccoli, and diced red bell pepper.",
+    "Top each bowl with sliced avocado and fresh cilantro for garnish.",
+    "Drizzle any remaining marinade over the bowls for added flavor.",
+    "Serve immediately and enjoy your healthy chicken bowl!"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a healthy chicken bowl featuring diced chicken breast, cooked quinoa, vibrant broccoli florets, diced red bell pepper, and sliced avocado, all beautifully arranged in a clean white ceramic bowl. The dish is garnished with fresh cilantro and drizzled with marinade, set on a light neutral surface. The composition fills 90–100% of the frame, showcasing clear food texture, with a shallow depth of field and soft natural daylight creating gentle shadows. The focus is sharp at the center of the food, captured from a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>chicken breast, quinoa, broccoli, bell pepper, avocado, olive oil, soy sauce, honey, garlic powder, cilantro, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521001/dc61432688f.png</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/d2da3517c3f.png</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/7bd66528cb9.png</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/dc546851fc6.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/68b3954ba66.png</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521001/62316ce4609.png</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/46626ea85e6.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/4befcf42cec.png</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/9f47bbe1313.png</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/41923041ba1.png</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Healthy Chicken Bowl Better Than Takeout
+## Introduction
+The Healthy Chicken Bowl is an exciting and nutritious dish that brings together a colorful array of ingredients to create a meal that is as satisfying as it is good for you. This recipe is ideal for anyone looking to enjoy a wholesome meal without sacrificing flavor. Combining protein-rich chicken, vibrant vegetables, and nutrient-dense quinoa, this bowl provides a balanced and hearty option that feels indulgent yet is packed with health benefits.
+Whether you're preparing for a busy week ahead or simply in search of a healthy dinner option to please the family, this bowl comes together in a flash, taking just 30 minutes from start to finish. With its delightful mix of flavors and textures, it’s perfect for serving on a weeknight or enjoying as a meal-prepped lunch that you can look forward to.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 15 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Healthy
+- Servings: 4
+- Calories: ~450 per serving
+This easy-to-follow recipe features tender marinated chicken served atop fluffy quinoa, accompanied by fresh broccoli florets and crunchy red bell pepper. Topped with creamy avocado slices and fragrant cilantro, each element enhances the others, resulting in a delicious dish that offers both comfort and nourishment. 
+## Ingredients
+- 1 lb boneless, skinless chicken breast, diced
+- 2 cups cooked quinoa
+- 1 cup broccoli florets
+- 1 red bell pepper, diced
+- 1 avocado, sliced
+- 2 tablespoons olive oil
+- 2 tablespoons soy sauce (low sodium)
+- 1 tablespoon honey
+- 1 teaspoon garlic powder
+- Salt and pepper to taste
+- Fresh cilantro for garnish
+With these simple yet powerful ingredients, you can create a meal that is satisfying and beneficial to your overall health. This dish effectively utilizes lean proteins, healthy fats, and fibrous vegetables, making it a nutritious option for anyone aiming for a balanced diet.
+{{image_ing_1}}
+## Instructions
+1. In a large bowl, combine olive oil, soy sauce, honey, garlic powder, salt, and pepper. Mix well to create a marinade.
+2. Add the diced chicken to the marinade and let it sit for at least 15 minutes.
+3. While the chicken marinates, steam the broccoli florets until they are tender, about 5-7 minutes.
+4. In a large skillet over medium heat, add the marinated chicken and cook for 6-8 minutes, or until fully cooked and golden brown.
+5. In serving bowls, layer the cooked quinoa, followed by the sautéed chicken, steamed broccoli, and diced red bell pepper.
+6. Top each bowl with sliced avocado and fresh cilantro for garnish.
+7. Drizzle any remaining marinade over the bowls for added flavor.
+8. Serve immediately and enjoy your healthy chicken bowl!
+## Nutritional Benefits
+### High Protein Content
+One of the standout features of this Healthy Chicken Bowl is its impressive protein content, primarily derived from the boneless, skinless chicken breast. Chicken breast is celebrated in the health and fitness community for its ability to provide ample protein while being low in fat, making it an ideal choice for building and repairing muscles. Each serving of this dish not only satisfies hunger but also supports your dietary goals, especially beneficial after workouts.
+### Rich in Healthy Fats
+Another key ingredient that enhances both the flavor and nutritional value of this dish is the avocado. Avocado is often praised for its healthy monounsaturated fats, which are a perfect addition to a balanced diet. These fats are known to promote heart health, prevent inflammation, and help the body absorb fat-soluble vitamins such as A, D, E, and K. By including slices of avocado on top of your chicken bowl, you enhance not only the flavor but also the overall health benefits of the meal.
+### Packed with Vitamins
+The fresh vegetables in this bowl—broccoli and red bell pepper—are nutritional powerhouses that provide a variety of essential vitamins and minerals. Broccoli is high in vitamins C and K, fiber, and various antioxidants, while red bell pepper is an excellent source of vitamin A and has incredibly high levels of vitamin C. Together, these vegetables add not only vibrant color and crunch but also enhance the dish's overall nutrient density, making it a fantastic choice for anyone looking to elevate their vegetable intake.
+## Preparation Steps
+### Marinating the Chicken
+Although marinating chicken is often seen as an optional step, it is critical in this recipe for building flavor and ensuring juiciness. Begin by combining the olive oil, low sodium soy sauce, honey, garlic powder, and a pinch of salt and pepper in a large bowl. Mixing these ingredients together will create a rich marinade that will infuse the chicken with flavor. Once mixed, add the diced chicken breast into the marinade, ensuring each piece is thoroughly coated. Allow this mixture to sit for at least 15 minutes to ensure the chicken absorbs the flavors.
+### Steaming the Broccoli
+While the chicken is marinating, the next step is to prepare the broccoli. Steaming is often the best method for preserving the vibrant color and nutrients of the vegetable. Take your broccoli florets and place them in a steaming basket over boiling water for about 5-7 minutes. The timing is key—remove the broccoli once it’s tender but still bright green to retain its optimal texture and taste.
+### Cooking the Chicken
+Once the chicken has marinated and the broccoli is steamed, it’s time to cook the chicken. Heat a large skillet over medium heat, add the marinated chicken, and allow it to cook for about 6-8 minutes. It’s essential to cook the chicken until it is golden brown and fully cooked to ensure safety and achieve that desirable texture. Using a skillet will give the chicken a nice sear, locking in the flavors of the marinade while keeping it juicy inside.
+## Assembling the Chicken Bowl
+### Layering the Ingredients
+Creating the perfect Healthy Chicken Bowl involves a thoughtful assembly of all the components to achieve a harmonious blend of textures and flavors. Start with a base of cooked quinoa in each serving bowl, which not only provides a nutritious foundation but also a neutral flavor that complements the other ingredients well. Aim for about half a cup of quinoa per bowl to ensure a satisfying portion without overwhelming the other elements.
+Next, follow this with a generous portion of the sautéed chicken. The golden-brown pieces will add a deliciously savory touch that elevates the entire dish. Ensure the chicken is evenly distributed across the quinoa so that every bite contains a burst of flavor.
+Once the chicken layer is established, add the steamed broccoli florets on top. Their bright green color not only enhances the visual appeal of the dish but also adds a valuable crunch and earthy taste. You can use about a cup of broccoli per bowl, ensuring a good balance stays intact.
+To top off the initial layers, include the diced red bell pepper around the bowl. These finely chopped pieces add a slight sweetness and vibrant color, further enriching the dish's presentation and flavor profile.
+### Finishing Touches
+After layering the main components, the finishing touches are what transform the dish into a gourmet experience. Each bowl should be adorned with slices of creamy avocado, which not only add healthy fats but also a rich texture that contrasts beautifully with the quinoa and chicken. Aim for about half an avocado per serving.
+Finally, don’t forget a sprinkle of fresh cilantro for garnish. This aromatic herb introduces a fresh pop that ties all of the flavors together, making the overall taste profile even more delightful. 
+To amplify the taste experience, drizzle any remaining marinade over the top of the bowls. This adds an extra layer of flavor and ensures that every bite is just as enjoyable as the first.
+## Serving Suggestions
+### Complementary Side Dishes
+While the Healthy Chicken Bowl is satisfying on its own, serving it alongside a light salad can enhance the overall meal experience. A simple mixed greens salad with a lemon vinaigrette is an excellent accompaniment, as it adds a refreshing contrast to the richer flavors of the chicken and quinoa.
+Alternatively, steamed vegetables such as asparagus or green beans can provide additional nutrients and fiber, creating a complete and fulfilling meal. Not only do they add variety, but they also help make use of seasonal produce, keeping the meal fresh and exciting.
+### Beverage Pairing
+The right beverage can enhance your dining experience significantly. A refreshing green tea serves as an excellent accompaniment, with its earthiness balancing the flavors in the bowl. You could also opt for infused water with slices of cucumber or lemon, as its lightness complements the freshness of the dish while aiding in digestion.
+## Storage Tips
+### Storing Leftovers
+One of the great advantages of the Healthy Chicken Bowl is its capacity for easy storage. To ensure that leftovers remain fresh, store each component separately in airtight containers. This method maintains the textures and flavors, allowing you to enjoy your bowl just as much during the next serving.
+The quinoa can be refrigerated for up to 4-5 days, while the marinated chicken can also last the same amount of time. Keep the avocado slices out until you’re ready to serve to prevent browning, and store any unused vegetables in a separate container.
+### Reheating Instructions
+When it comes to reheating your chicken bowl, aim for gentle methods to preserve the integrity of the ingredients. The microwave is a convenient tool for warming up, but be sure to cover the bowl to retain moisture. A few minutes at medium heat should suffice, but check frequently to avoid overheating.
+Another option is to reheat the chicken and vegetables in a skillet over low heat, allowing their flavors to meld together while bringing them back to the desired temperature. Be attentive to the quinoa, as it is best served just warm to preserve its fluffy texture.
+## Flavor Variations
+### Changing the Protein
+For those seeking a vegetarian option, substituting the chicken with tofu or beans can create a delectable alternative. Tofu provides a similar texture, allowing it to soak up the flavors of the marinade while remaining a solid protein source. Alternatively, you can consider using chickpeas, which offer both protein and fiber, ensuring well-rounded nutrition.
+### Experimenting with Vegetables
+Don’t hesitate to explore different vegetables to bring new life to your Healthy Chicken Bowl. Snap peas, carrots, or zucchini can be delightful additions, contributing crunch and a mix of colors to your dish. Experimenting with seasonal vegetables also adds an exciting twist, helping to keep your meals varied and interesting.
+## Meal Prep Ideas
+### Batch Cooking
+Preparing multiple servings of the Healthy Chicken Bowl at once can be a lifesaver for busy weeks. By batch cooking, you can fill your fridge with healthy lunches or dinners that are ready to go. Consider cooking twice the amount of quinoa and chicken, then portioning them out per serving to streamline the process for the whole week.
+### Customizing Individual Bowls
+One of the great aspects of this chicken bowl is its adaptability. You can easily customize each bowl according to personal preferences or dietary restrictions, which makes it appealing for families with varied tastes. For example, you could incorporate different dressings or alternate toppings to suit individual preferences, ensuring that everyone enjoys their meal.
+## Serving Size and Calories
+### Portion Control
+Each Healthy Chicken Bowl serves about 4 people, with each serving containing approximately 450 calories. This balance makes it suitable for those looking to maintain a healthy diet without sacrificing flavor. It’s an accessible option for both lunch and dinner, fitting into various dietary requirements.
+### Satiating Enough?
+The thoughtful combination of protein from the chicken, healthy fats from the avocado, and fiber-rich quinoa ensures that you'll feel satisfied after enjoying this meal. The dish is designed to keep you energized without feeling overly full, making it an excellent choice for any time of day.
+## Conclusion
+The Healthy Chicken Bowl stands out as a nourishing meal that marries flavor and health. This dish can easily be prepared within 30 minutes, making it ideal for those with busy schedules. The blend of fresh ingredients and delightful textures ensures a satisfying experience, leaving diners both pleased and revitalized.
+</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl Better Than Takeout</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Easy Healthy Chicken Bowl Recipe for a Nutritious Dinner at Home</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Flavor-Packed Healthy Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Create a flavorful and nutritious dinner at home with this easy healthy chicken bowl recipe. Packed with wholesome ingredients like quinoa and topped with creamy avocado, this meal is perfect for meal prep or a cozy night in. Enjoy a delicious way to nourish your body while savoring the vibrant tastes of fresh ingredients.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>healthy chicken bowl, quinoa recipe, easy dinner, meal prep, nutritious ingredients, avocado topping</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Enjoy a Healthy Chicken Bowl that's better than takeout! Quick, tasty, and packed with nourishing ingredients. 🍲🥗</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A1-Pinterest_01-out/output_images/image_2.jpg</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/healthy-chicken-bowl-better-than-takeout-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Quick High Protein Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quick High Protein Chicken Meal Prep 🍗💪
+Ingredients:
+- 1 pound boneless, skinless chicken breasts
+- 1 cup quinoa, rinsed
+- 2 cups broccoli florets
+- 1 tablespoon olive oil
+- 1 teaspoon garlic powder
+- 1 teaspoon paprika
+- Salt and pepper to taste
+- 1 lemon, juiced
+Instructions:
+1. Preheat the oven to 400°F (200°C).
+2. In a mixing bowl, toss the chicken breasts with olive oil, garlic powder, paprika, salt, and pepper.
+3. Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through.
+4. While the chicken is baking, bring 2 cups of water to a boil in a saucepan. Add the quinoa, reduce heat, cover, and simmer for 15 minutes or until water is absorbed.
+5. In a separate pot, steam the broccoli florets for about 5-7 minutes until bright green and tender.
+6. Once the chicken is done, let it rest for a few minutes, then slice it into strips.
+7. Fluff the cooked quinoa with a fork and mix in the lemon juice.
+8. Divide the quinoa, broccoli, and chicken evenly into meal prep containers.
+9. Store in the refrigerator for up to 4 days.
+Prep Time: 10 minutes
+Cook Time: 30 minutes
+Total Time: 40 minutes
+Course: Meal Prep
+Cuisine: American
+Servings: 4
+Calories: ~400 per serving</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Quick High Protein Chicken Meal Prep",
+  "summary": "This meal prep recipe features high-protein chicken breasts paired with quinoa and broccoli for a nutritious and easy-to-make dish. Perfect for a week of healthy lunches.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "30",
+  "total_time": "40",
+  "calories": "400",
+  "course": "Main Course",
+  "cuisine": "American",
+  "keywords": [
+    "meal prep",
+    "chicken",
+    "quinoa",
+    "broccoli",
+    "high protein",
+    "healthy",
+    "easy"
+  ],
+  "notes": "Store in the refrigerator for up to 4 days. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "pound",
+      "name": "boneless, skinless chicken breasts"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "quinoa"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "broccoli florets"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "paprika"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "1",
+      "unit": "",
+      "name": "lemon, juiced"
+    }
+  ],
+  "instructions": [
+    "Preheat the oven to 400°F (200°C).",
+    "In a mixing bowl, toss the chicken breasts with olive oil, garlic powder, paprika, salt, and pepper.",
+    "Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through.",
+    "While the chicken is baking, bring 2 cups of water to a boil in a saucepan.",
+    "Add the quinoa, reduce heat, cover, and simmer for 15 minutes or until water is absorbed.",
+    "In a separate pot, steam the broccoli florets for about 5-7 minutes until bright green and tender.",
+    "Once the chicken is done, let it rest for a few minutes, then slice it into strips.",
+    "Fluff the cooked quinoa with a fork and mix in the lemon juice.",
+    "Divide the quinoa, broccoli, and chicken evenly into meal prep containers."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a meal prep container filled with sliced grilled chicken breast, fluffy quinoa mixed with lemon juice, and vibrant green broccoli florets. The food is arranged neatly in a clean white ceramic bowl with a slight 3/4 angle, on a light neutral surface. The composition fills 90% of the frame, showcasing the clear textures of the ingredients with a shallow depth of field and soft natural daylight illuminating the dish, creating gentle shadows. Sharp focus at the center of the food. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>chicken, quinoa, broccoli, olive oil, garlic powder, paprika, lemon, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521001/2586e095025.png</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/ba1bd841938.png</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/4380dad8be2.png</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/d0f702e1a9b.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/af1e47e6948.png</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521001/085a200dd91.png</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/d342ff07245.png</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/f066c23a2b9.png</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/adc5adbc238.png</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/8f483769afc.png</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Quick High Protein Chicken Meal Prep Recipe
+## Introduction
+In today's fast-paced world, the significance of meal prepping cannot be overstated; it allows busy individuals to stay committed to healthy eating without the hassle of daily cooking. The Quick High Protein Chicken Meal Prep recipe stands out in this arena, offering a nourishing option that is both convenient to prepare and satisfying to eat. This meal is particularly ideal for those looking to maintain energy levels throughout the day while enjoying a balanced diet.
+The combination of boneless, skinless chicken breasts with nutrient-dense quinoa and vibrant broccoli makes for a colorful dish packed with flavor and essential nutrients. Whether you're meal prepping for the week, in need of a quick dinner solution, or simply looking to stay aligned with your dietary goals, this recipe has got you covered. The ease of preparation paired with the nutritional benefits makes this dish an excellent choice for anyone.
+With its high protein content and wholesome ingredients, the Quick High Protein Chicken Meal Prep not only fulfills nutritional needs but also provides a sense of satisfaction with each bite. Let's explore this recipe in detail to arm you with all the knowledge you need to prepare it with confidence.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 30 minutes
+- Total Time: 40 minutes
+- Course: Meal Prep
+- Cuisine: American
+- Servings: 4
+- Calories: ~400 per serving
+This delicious meal prep recipe is designed to deliver a well-rounded approach to healthy eating through the delightful interplay of flavors and textures. With a quick total time of just 40 minutes, you can prepare a week's worth of meals in a breeze. The simplicity of the ingredient list highlights the focus on wholesome and nutritious components that come together to create a satisfying dish.
+## Ingredients
+To prepare the Quick High Protein Chicken Meal Prep, you will need the following ingredients:
+- 1 pound boneless, skinless chicken breasts
+- 1 cup quinoa, rinsed
+- 2 cups broccoli florets
+- 1 tablespoon olive oil
+- 1 teaspoon garlic powder
+- 1 teaspoon paprika
+- Salt and pepper to taste
+- 1 lemon, juiced
+{{image_ing_1}}
+## Instructions
+1. Preheat the oven to 400°F (200°C).
+2. In a mixing bowl, toss the chicken breasts with olive oil, garlic powder, paprika, salt, and pepper.
+3. Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through.
+4. While the chicken is baking, bring 2 cups of water to a boil in a saucepan. Add the quinoa, reduce heat, cover, and simmer for 15 minutes or until water is absorbed.
+5. In a separate pot, steam the broccoli florets for about 5-7 minutes until bright green and tender.
+6. Once the chicken is done, let it rest for a few minutes, then slice it into strips.
+7. Fluff the cooked quinoa with a fork and mix in the lemon juice.
+8. Divide the quinoa, broccoli, and chicken evenly into meal prep containers.
+9. Store in the refrigerator for up to 4 days.
+## Preparation Method
+Understanding the preparation method is key to making any recipe successful. Here’s how to prepare this meal effectively:
+### Preheating the Oven
+To begin with, set your oven to 400°F (200°C). It is crucial that the oven reaches this temperature prior to baking the chicken; this ensures even cooking and helps to retain moisture in the meat, avoiding dryness.
+### Preparing the Chicken
+Next, in a mixing bowl, combine the boneless, skinless chicken breasts with one tablespoon of olive oil, one teaspoon of garlic powder, one teaspoon of paprika, along with salt and pepper to taste. It’s important to ensure each chicken breast is thoroughly coated with this mixture, as it infuses flavor into the meat. The garlic powder and paprika will not only add taste but also a rich coloration when cooked.
+### Baking the Chicken
+Once the chicken is well coated, arrange the seasoned breasts on a baking sheet. The chicken should be spread out in a single layer to facilitate even cooking. Place the baking sheet in the preheated oven and bake for 20 to 25 minutes, or until the chicken is thoroughly cooked, with juices running clear when pierced. This step is vital for achieving perfectly tender chicken that complements the rest of the dish.
+## Cooking Quinoa
+Quinoa acts as a perfect base for this meal, contributing both texture and protein. Here is how to prepare it effectively:
+### Rinsing the Quinoa
+Prior to cooking, it’s essential to rinse the quinoa under cold water in a fine mesh strainer. This step removes saponins, which can lend a bitter taste to the grains. Rinsing will leave you with a nutty and pleasant flavor once cooked.
+### Cooking the Quinoa
+Bring 2 cups of water to a vigorous boil in a saucepan. Once boiling, add the rinsed quinoa. After adding the quinoa, reduce the heat to a simmer, cover the saucepan, and allow it to cook for about 15 minutes. You will know that the quinoa is ready when the water is absorbed and the grains appear translucent with tiny "tails" curling around them.
+## Steaming the Broccoli
+Broccoli not only adds nutritional benefits to the meal but also provides a refreshing crunch.
+### Preparing the Broccoli
+Start by washing and cutting the broccoli into small florets. This ensures that they will cook evenly and become tender without losing their vibrant green color.
+### Steaming Process
+In a separate pot, add a small amount of water and place a steaming basket inside (or use a pot with a lid). Steam the broccoli florets for about 5 to 7 minutes until they are bright green and tender, ensuring they do not overcook. Steaming retains most of the broccoli's nutrients while giving it a delightful, crisp-tender texture that balances well with the other components of the meal.
+By following these detailed steps, you will create a nourishing lunch or dinner option that can be enjoyed throughout the week. This method not only saves time but enhances your meal prep experience, ensuring deliciousness is only minutes away.
+baking process for a truly one-pan meal prep. This can save time and reduce cleanup while allowing the flavors from the chicken to enhance the broccoli.
+### Prep Ahead of Time
+- If your schedule permits, consider preparing the chicken and quinoa ahead of time. You can marinate the chicken overnight for added flavor or cook a larger batch of quinoa to use in other meals throughout the week.
+## Assembling the Meal Prep
+After cooking the chicken, quinoa, and broccoli, it’s time to assemble your meal prep containers in a way that maximizes both flavor and aesthetics.
+### Slicing the Chicken
+Once the chicken is baked, allow it to rest for a few minutes to retain its juices. Using a sharp knife, slice it into strips that are about ½ inch thick. This not only makes the chicken easier to eat but also allows for even distribution across the meal prep containers. 
+### Fluffing the Quinoa
+Take a fork and fluff the cooked quinoa gently. This helps separate the grains and improves the texture, making it more pleasant to eat. After fluffing, pour the freshly squeezed lemon juice over the quinoa and toss it lightly. The acidity from the lemon juice adds a refreshing brightness that balances the dish perfectly.
+### Dividing into Containers
+With everything prepared, it's time to fill your meal prep containers. Start by placing a generous scoop of the lemon-infused quinoa into each container. Next, add a portion of broccoli beside the quinoa; aim for an even distribution so that each meal contains a balanced ratio of all components. Finally, lay the sliced chicken atop the quinoa and broccoli for a visually appealing meal that is not only nutritious but also inviting.
+## Storage Instructions
+Proper storage is key to maintaining the freshness and quality of your meal prep. 
+### Refrigeration Tips
+Store the filled meal prep containers in the refrigerator, ensuring they are well-sealed to prevent contamination and moisture loss. These meals can be kept for up to four days without losing quality, making them ideal for planning your week ahead.
+### Reheating Guidelines
+When you're ready to enjoy your meal, simply pop a container into the microwave and heat until warm, adjusting the heating time as necessary, depending on your microwave’s power level. For best results, cover the container loosely during reheating to prevent splatters while maintaining moisture.
+## Nutritional Benefits
+Understanding the nutritional benefits of this dish enhances its appeal and showcases its value as a healthy meal option. 
+### High Protein Content
+The chicken serves as a primary source of lean protein, essential for muscle repair and growth. High-protein meals like this one can help maintain muscle mass, especially beneficial for those engaged in regular physical activity.
+### Whole Grains
+Quinoa is often hailed as a superfood due to its designation as a complete protein. It contains all nine essential amino acids and is packed with fiber, which aids in digestion and promotes a feeling of fullness. This makes quinoa an excellent base for meal prep, providing sustained energy and supporting gut health.
+### Rich in Vegetables
+Don’t overlook the health benefits of the broccoli included in this dish. This vibrant green vegetable is a powerhouse of vitamins, notably vitamins C and K, and is rich in antioxidants. Including vegetables in your meals is crucial for a balanced diet, and broccoli's fiber content contributes to overall digestive health.
+## Flavor Variations
+To keep your meal prep interesting, consider incorporating various flavor adjustments to suit your taste buds. 
+### Spice Up the Chicken
+One way to change things up is by experimenting with different spices or marinades for the chicken. Aside from the garlic powder and paprika, you might use a blend of chili powder and cumin for a Southwestern twist or a mixture of soy sauce and ginger for an Asian-inspired flair.
+### Alternate Grains
+For those wishing to change the texture or flavor profile, swapping quinoa for other whole grains, such as brown rice or farro, can yield delightful results. Each grain has its unique taste and nutritional benefits, allowing you to tailor your meal according to your preferences.
+## Meal Prep Tips
+A few tried-and-true tips can make the meal prep process smoother and more efficient. 
+### One-Pan Cooking
+For a truly time-efficient method, consider roasting the broccoli on the same pan as the chicken during the baking process. This not only saves time but also enhances the flavor of the broccoli by allowing it to absorb some of the juices released from the chicken.
+### Prep Ahead of Time
+If your schedule allows, prepping the chicken and quinoa in advance can significantly streamline your meal prep routine. Marinating the chicken overnight can infuse even deeper flavors, while cooking extra quinoa can be useful for various meals beyond this specific recipe.
+## Conclusion
+The Quick High Protein Chicken Meal Prep offers a balanced and nutritious option for anyone looking to incorporate ease and health into their weekly meal planning. With its high protein content, whole grains, and nutrient-rich vegetables, it stands as a versatile recipe that can adapt to various tastes and preferences. Enjoying wholesome meals doesn’t have to be complicated or time-consuming, making this dish a great choice for meal prep enthusiasts.
+</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Quick High Protein Chicken Meal Prep Recipe</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Meal Prep for Quick Healthy Weeknight Dinners</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Flavorful Protein-Packed Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Discover how easy it is to make high protein chicken meal prep for quick and healthy weeknight dinners. With tender chicken breast and nutrient-rich quinoa, this meal prep recipe is perfect for busy evenings when you want something nutritious and satisfying. Enjoy the convenience of having delicious meals ready to go, making healthy choices easier than ever.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>high protein, meal prep, chicken breast, quinoa, healthy, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Quick high protein chicken meal prep: Delicious, healthy, and easy to make in just 40 minutes for meal prep perfection!</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A1-Pinterest_01-out/output_images/image_3.jpg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/quick-high-protein-chicken-meal-prep-recipe-2/</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-high-protein-chicken-bowl-2/</t>
+          <t>https://lowcarbdaily.com/easy-high-protein-chicken-bowl-5/</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/healthy-chicken-bowl-better-than-takeout-3/</t>
+          <t>https://lowcarbdaily.com/healthy-chicken-bowl-better-than-takeout-6/</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/quick-high-protein-chicken-meal-prep-recipe-2/</t>
+          <t>https://lowcarbdaily.com/quick-high-protein-chicken-meal-prep-recipe-5/</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-high-protein-chicken-bowl-5/</t>
+          <t>https://lowcarbdaily.com/easy-high-protein-chicken-bowl-6/</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/healthy-chicken-bowl-better-than-takeout-6/</t>
+          <t>https://lowcarbdaily.com/healthy-chicken-bowl-better-than-takeout-7/</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/quick-high-protein-chicken-meal-prep-recipe-5/</t>
+          <t>https://lowcarbdaily.com/quick-high-protein-chicken-meal-prep-recipe-6/</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,7 +708,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523162/0cf58ea01b7.png</t>
@@ -739,7 +738,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -904,7 +902,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523165/5c406c84db3.png</t>
@@ -935,7 +932,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1112,7 +1108,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523214/9e559e93e93.png</t>
@@ -1143,7 +1138,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1312,7 +1306,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523165/fa5208d8215.png</t>
@@ -1343,7 +1336,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1516,7 +1508,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523173/a7ab30c3539.png</t>
@@ -1547,7 +1538,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1714,7 +1704,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523160/8dfe5ba75e1.png</t>
@@ -1745,7 +1734,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1910,7 +1898,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523161/e3e3f71c145.png</t>
@@ -1941,7 +1928,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2113,7 +2099,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523161/3c364b1180f.png</t>
@@ -2144,7 +2129,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2320,7 +2304,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523163/500f1a9d1d9.png</t>
@@ -2349,181 +2332,6 @@
       <c r="S10" t="inlineStr">
         <is>
           <t>DONE</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Healthy Chicken Dinner Under 30 Minutes</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Healthy Chicken Dinner Under 30 Minutes 🍗🥗
-Ingredients:
-- 2 boneless, skinless chicken breasts
-- 1 tablespoon olive oil
-- 2 cups fresh spinach
-- 1 cup cherry tomatoes, halved
-- 1 teaspoon garlic powder
-- 1 teaspoon Italian seasoning
-- Salt and pepper to taste
-- 1/4 cup feta cheese, crumbled (optional)
-Instructions:
-1. Heat the olive oil in a large skillet over medium-high heat.
-2. Season the chicken breasts with garlic powder, Italian seasoning, salt, and pepper.
-3. Add the chicken to the skillet and cook for 6-7 minutes on each side until golden brown and cooked through.
-4. Remove the chicken from the skillet and let it rest for a couple of minutes.
-5. In the same skillet, add the cherry tomatoes and spinach, cooking until the spinach is wilted and tomatoes are softened, about 3-4 minutes.
-6. Slice the chicken and return it to the skillet, mixing it with the vegetables.
-7. If desired, sprinkle feta cheese on top before serving.
-8. Serve warm and enjoy your healthy meal!
-Prep Time: 10 minutes
-Cook Time: 15 minutes
-Total Time: 25 minutes
-Course: Main Course
-Cuisine: American
-Servings: 2
-Calories: ~400 per serving</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-05-23 16:47:52</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{
-  "name": "Healthy Chicken Dinner Under 30 Minutes",
-  "summary": "This quick and healthy chicken dinner features tender chicken breasts paired with fresh spinach and cherry tomatoes. It's a nutritious meal ready in under 30 minutes.",
-  "servings": "2",
-  "prep_time": "10",
-  "cook_time": "15",
-  "total_time": "25",
-  "calories": "400",
-  "course": "Main Course",
-  "cuisine": "American",
-  "keywords": [
-    "chicken",
-    "healthy",
-    "quick",
-    "dinner",
-    "spinach",
-    "tomatoes"
-  ],
-  "notes": "Feel free to add more vegetables or adjust seasonings to your taste. Calories are per serving.",
-  "ingredients": [
-    {
-      "amount": "2",
-      "unit": "pieces",
-      "name": "boneless, skinless chicken breasts"
-    },
-    {
-      "amount": "1",
-      "unit": "tablespoon",
-      "name": "olive oil"
-    },
-    {
-      "amount": "2",
-      "unit": "cups",
-      "name": "fresh spinach"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "cherry tomatoes, halved"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "garlic powder"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "Italian seasoning"
-    },
-    {
-      "amount": "",
-      "unit": "",
-      "name": "Salt and pepper to taste"
-    },
-    {
-      "amount": "¼",
-      "unit": "cup",
-      "name": "feta cheese, crumbled (optional)"
-    }
-  ],
-  "instructions": [
-    "Heat the olive oil in a large skillet over medium-high heat.",
-    "Season the chicken breasts with garlic powder, Italian seasoning, salt, and pepper.",
-    "Add the chicken to the skillet and cook for 6-7 minutes on each side until golden brown and cooked through.",
-    "Remove the chicken from the skillet and let it rest for a couple of minutes.",
-    "In the same skillet, add the cherry tomatoes and spinach, cooking until the spinach is wilted and tomatoes are softened, about 3-4 minutes.",
-    "Slice the chicken and return it to the skillet, mixing it with the vegetables.",
-    "If desired, sprinkle feta cheese on top before serving.",
-    "Serve warm and enjoy your healthy meal!"
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a healthy chicken dinner featuring sliced golden-brown chicken breasts on a bed of wilted spinach and softened cherry tomatoes, sprinkled with crumbled feta cheese. Serve in a clean white ceramic bowl on a light neutral surface, tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at food center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>chicken, olive oil, spinach, cherry tomatoes, garlic powder, Italian seasoning, salt, pepper, feta cheese, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle stone or light wood texture, soft natural daylight, minimal shadows, minimal styling, food photography, no text, no logos, no packaging, kitchen or neutral surface only --ar 1:1 --v 6.1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0523163/ed514dd6185.png</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523163/a0941b1576f.png</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523163/198ec7b0cf9.png</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523163/d63fa6f2278.png</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523163/bd6dc554f0c.png</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>task status failed: {'errorDetails': "Your request was flagged by Midjourney content moderation. The message was deleted by Discord (ephemeral moderation). Please review Midjourney's content policy and try a different pr</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,86 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>error_ing</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statut Article</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_article</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_title_pin</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_keywords</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_focus_keyword</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_pillar_content</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_image</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_url</t>
         </is>
       </c>
     </row>
@@ -708,6 +788,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523162/0cf58ea01b7.png</t>
@@ -736,6 +817,171 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy High Protein Chicken Bowl You’ll Love
+## Introduction
+The Easy High Protein Chicken Bowl is a nourishing and colorful dish that brings together the finest ingredients for a delightful meal. This recipe is perfect for anyone looking to boost their protein intake while enjoying a variety of flavors and textures. With tender chicken breast, a nutty base of quinoa, and fresh vegetables, this bowl is more than just fulfilling; it's a feast for the eyes and the palate. 
+This dish is quite versatile, catering to those busy weeknights when you're looking for a quick dinner solution, or even as a meal prep option to savor throughout the week. Imagine coming home from a long day and whipping up a wholesome meal in just about 30 minutes – that’s the magic of this chicken bowl. The colorful ingredients not only create an enticing visual appeal but also ensure your nutrition needs are met without compromising on flavor. 
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 20 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: American
+- Servings: 4
+- Calories: ~450 per serving
+This high-protein chicken bowl combines tender chicken breast, wholesome quinoa, vibrant vegetables, and creamy avocado for a satisfying main course. Ready in just 30 minutes, it's perfect for quick dinners or meal prep for the week ahead. Whether you're a fitness enthusiast or simply enjoy delicious food, this chicken bowl is sure to please.
+## Ingredients
+### The dish’s core ingredients include:
+- 1 lb boneless, skinless chicken breast, diced
+- 1 cup quinoa, rinsed and drained
+- 2 cups vegetable broth
+- 1 cup cherry tomatoes, halved
+- 1 cup black beans, drained and rinsed
+- 1 cup corn kernels (fresh or frozen)
+- 1 avocado, sliced
+- 2 tablespoons olive oil
+- 1 teaspoon chili powder
+- Salt and pepper to taste
+- Fresh cilantro for garnish
+{{image_ing_1}}
+## Instructions
+1. In a medium pot, bring the vegetable broth to a boil. Add the quinoa, reduce heat to low, cover, and simmer for about 15 minutes or until the quinoa is fluffy and the liquid is absorbed.
+2. While the quinoa is cooking, heat olive oil in a large skillet over medium heat. Add the diced chicken breast and season with chili powder, salt, and pepper.
+3. Cook the chicken for about 6-8 minutes, stirring occasionally, until fully cooked and no longer pink in the center.
+4. Once the chicken is cooked, stir in the cherry tomatoes, black beans, and corn. Cook for an additional 3-4 minutes until everything is heated through.
+5. Fluff the cooked quinoa with a fork and divide it among serving bowls.
+6. Top each bowl with the chicken mixture and sliced avocado.
+7. Garnish with fresh cilantro and additional salt and pepper if desired.
+8. Serve warm and enjoy your high-protein chicken bowl!
+## Cooking Preparation
+Understanding proper preparation is essential for achieving the best results in your Easy High Protein Chicken Bowl. Each step ensures that flavors combine beautifully and textures are pleasingly varied.
+### Choosing the Right Chicken
+Selecting fresh, high-quality chicken breast is crucial for this dish. Look for chicken that is pink and firm to the touch, with no bruises or discoloration. If possible, purchase organic or free-range chicken for the best flavor and nutritional value. After purchasing, store chicken in the coldest part of your refrigerator and use it within a couple of days, or freeze it for longer storage. Proper handling of the chicken ensures a safe and delicious meal at the end.
+### Preparing Quinoa
+Rinsing and draining quinoa correctly is a critical step in preparing it properly. Quinoa has a natural coating called saponin, which can impart a bitter taste if not washed away. To rinse the quinoa, place it in a fine-mesh strainer and run it under cold water, shaking the strainer to ensure all grains are rinsed. Once rinsed, allow it to drain for a moment before adding it to the boiling vegetable broth. This extra effort helps enhance the overall flavor and texture of the finished dish, allowing the quinoa to absorb the rich broth as it cooks.
+### Vegetable Preparation
+When it comes to vegetable preparation, even chopping is essential for uniform cooking. For this recipe, focus on halving the cherry tomatoes and slicing the avocado. Uniform cuts help ensure that all vegetables cook evenly and provide a pleasant texture throughout the dish. The fresh, juicy burst of cherry tomatoes adds a lovely contrast to the seasoned chicken, while the creamy avocado lends a rich mouthfeel that ties all the flavors together beautifully.
+## Cooking Methods
+Several techniques ensure that the protein bowl is cooked to perfection. Mastering these methods will not only improve the final outcome of your dish but also boost your culinary skills.
+### Boiling Quinoa
+Boiling quinoa in vegetable broth rather than water enhances its flavor significantly. Begin by bringing the broth to a boil, then introduce the rinsed quinoa. Once you lower the heat, cover the pot and allow the quinoa to simmer. Cook until the grains are fluffy and the broth is absorbed, typically about 15 minutes. Fluffing quinoa with a fork after cooking helps separate the grains, ensuring a light and airy texture that's delightful in your bowl.
+### Sautéing Chicken
+Sautéing chicken properly is crucial for retaining juiciness and achieving flavor development. When heating the olive oil in the skillet, ensure it reaches a medium temperature before introducing the diced chicken. This step helps achieve a nice sear on the chicken breast, locking in moisture. As the chicken cooks, season it with chili powder, salt, and pepper to create a balanced flavor profile. Stir the chicken occasionally to promote even cooking and prevent sticking to the pan. The key to perfectly cooked chicken is to avoid overcrowding the pan, allowing each piece enough space to sauté effectively.
+### Assembling the Bowl
+Assembling your Easy High Protein Chicken Bowl is where the dish comes to life. Start by fluffing the quinoa and dividing it among serving bowls as the base. Next, top each bowl with the vibrant mixture of cooked chicken, cherry tomatoes, black beans, and corn. Finally, add a generous slice of avocado on top, and garnish with fresh cilantro. This layering technique not only maximizes flavor with every bite but also creates an appealing presentation that’s sure to impress whether enjoyed at home or served to guests.
+### Herb Garnish
+Fresh cilantro is more than just a visual accent in the Easy High Protein Chicken Bowl; it plays a significant role in enhancing the dish's overall flavor profile. The bright, slightly peppery flavor of cilantro balances the richness of the chicken and the creaminess of the avocado. Its herbaceous notes elevate the entire dish, making each bite fresher and more vibrant. Additionally, cilantro is known for its health benefits; it contains antioxidants and may aid digestion, making it a smart choice to include in this protein-packed meal.
+### Additional Seasonings
+Salt and pepper are fundamental seasoning components in this recipe, enhancing the natural flavors of the ingredients without overwhelming them. Salt is essential for bringing out the umami in the chicken while also allowing the flavors of the beans and vegetables to shine through. For those looking to lower their sodium intake, there are alternatives such as herbal seasonings or salt-free spice blends. Experimenting with garlic powder, onion powder, or even smoked paprika can provide flavorful options without the added sodium.
+## Nutritional Benefits
+This Easy High Protein Chicken Bowl is not just a delicious meal; it is also packed with nutritional benefits from its varied ingredients. Each component contributes essential nutrients and aids in maintaining a balanced diet.
+### Chicken (Protein Source)
+The chicken breast is the star for protein content in this dish, delivering approximately 31 grams of protein per serving. Protein is paramount for muscle repair, growth, and overall bodily functions. A diet rich in protein aids in weight management, as it promotes feelings of satiety and helps maintain muscle mass during weight loss. Additionally, chicken is an excellent source of B vitamins, which assist in energy production and maintaining a healthy metabolism.
+### Quinoa (Complete Protein)
+Quinoa distinguishes itself among grains due to its status as a complete protein—meaning it contains all nine essential amino acids that the body cannot produce on its own. This makes it an ideal option for both vegetarians and meat eaters alike. Quinoa is also gluten-free, making it suitable for those with gluten sensitivities. Furthermore, it is rich in fiber, iron, and magnesium, contributing to heart health, digestive wellness, and increased energy levels.
+### Beans and Corn (Fiber and Nutrients)
+Black beans and corn not only add delightful textures to the chicken bowl, but they also enrich the dish with dietary fiber and essential vitamins. Fiber is crucial for digestive health, helping to maintain regularity and support a balanced gut microbiome. Black beans, in particular, are an excellent source of plant-based protein, further enhancing the protein content of the meal. Meanwhile, corn provides notable amounts of vitamin C, folate, and antioxidants, which bolster the immune system and promote skin health.
+## Meal Prep &amp; Storage
+In a fast-paced world, meal prepping is an effective way to save time while ensuring that nutritious options are at the ready. This chicken bowl is a great candidate for meal prep, being easy to scale up and store for future meals.
+### Storing Leftovers
+To keep the Easy High Protein Chicken Bowl fresh, it's crucial to store leftovers properly. Allow the bowl to cool before transferring it to airtight containers. Depending on how you prefer to store, you can separate the chicken mix from the quinoa and toppings like avocado and cilantro, as these can become mushy. Stored correctly in the refrigerator, the chicken bowl can remain fresh for up to 3 days.
+### Reheating Techniques
+When reheating leftovers, it’s essential to maintain the textures and flavors. The microwave is quick and convenient; simply heat in 30-second intervals, stirring in between to ensure even warming. Alternatively, reheating on the stovetop in a non-stick pan over low heat will allow you to regain some of the dish’s original warmth and texture. If the chicken bowl seems dry, splash a bit of vegetable broth or water into the pan to keep things juicy.
+### Meal Prep Tips
+For those looking to maximize their meal prep experience, consider making a large batch of quinoa and chicken mixture on the weekend. This can be stored in individual portions, making it easy to assemble a quick meal during the week. Pre-chop other ingredients such as tomatoes, black beans, and corn, storing them separately in sealed bags or containers. When ready to eat, simply heat the chicken mixture and combine it with the fresh ingredients, resulting in a wholesome meal in mere minutes.
+## Serving Suggestions
+While the Easy High Protein Chicken Bowl is a fulfilling dish on its own, complementing it with thoughtful pairings can enhance your dining experience. 
+### Pairing with Sides
+To create a more substantial meal, consider serving the chicken bowl with a light green salad topped with a simple vinaigrette, incorporating additional vegetables like bell peppers or cucumbers for crunch. Homemade garlic bread or cornbread could also serve as hearty carb complements, soaking up any juices from the bowl, making every bite satisfying.
+### Beverage Pairings
+Selecting the right beverage can elevate your dining experience. Light drinks such as herbal teas or sparkling water infused with citrus make excellent pairings, enhancing the freshness of the chicken bowl without overpowering its flavors. A refreshing glass of lemonade can also provide a zesty contrast, balancing the meal's richness.
+## Variations
+One of the great aspects of the Easy High Protein Chicken Bowl is its versatility. Whether accommodating dietary preferences or personal tastes, variations can be seamlessly integrated.
+### Vegetarian Alternatives
+For a vegetarian twist on this dish, replacing the chicken with a plant-based protein such as tofu or tempeh offers a similar texture while maintaining the protein content. Marinate tofu in olive oil and spices before cooking to replicate the savory flavors of the original recipe. 
+### Different Grain Options
+Although quinoa serves as an excellent base, experimenting with other grains can yield interesting flavor profiles. Brown rice or farro are nutritious alternatives that add complexity to the dish, offering new texture and taste dimensions.
+### Additional Vegetables
+Incorporating seasonal vegetables not only adds nutritional value but also allows you to modify the dish according to your taste preferences. Roasted bell peppers, zucchini, or asparagus can provide an extra layer of flavor while making the chicken bowl even more colorful and appealing.
+## Conclusion
+The Easy High Protein Chicken Bowl is a balanced meal that combines a variety of textures and flavors, making it both satisfying and delicious. With a total preparation and cooking time of just 30 minutes and an approximate calorie count of 450 per serving, it's an excellent choice for any busy lifestyle. Enjoy the wholesome freshness of this recipe that fuels your day.
+</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Bowl You’ll Love</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Healthy High Protein Chicken Bowl Recipe with Quinoa and Avocado</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Savory High-Protein Chicken Quinoa Bowl</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Discover a healthy high protein chicken bowl recipe that combines tender chicken, quinoa, and creamy avocado for a satisfying meal. This nutritious dish is perfect for meal prep, offering a delicious taste of American cuisine that will keep you energized throughout the week. Enjoy this wholesome bowl as a vibrant way to nourish your body and taste buds.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>high protein, chicken bowl, quinoa, healthy recipe, meal prep, American cuisine</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Enjoy this Easy High Protein Chicken Bowl packed with flavor and nutrition! Perfect for a quick, satisfying meal.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_1.jpg</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/easy-high-protein-chicken-bowl-youll-love/</t>
         </is>
       </c>
     </row>
@@ -902,6 +1148,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523165/5c406c84db3.png</t>
@@ -930,6 +1177,172 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Minute High Protein Chicken Dinner
+## Introduction
+In today's fast-paced world, finding a meal that is both nutritious and quick to prepare can be a challenge. The 20-Minute High Protein Chicken Dinner is an ideal option, especially for busy weeknights when you crave a satisfying yet healthy dish without spending hours in the kitchen. With its delightful combination of tender boneless chicken breasts, vibrant broccoli florets, and fluffy quinoa, this recipe ensures that you don’t compromise on flavor or nutrition.
+This dish shines not just for its taste but also for its health benefits. High in protein, it caters to fitness enthusiasts and anyone aiming to maintain a healthy lifestyle. Protein is crucial for muscle repair and growth, making this meal an excellent choice for post-workout nourishment or a hearty family dinner. Moreover, the bright colors of broccoli and the nutty flavor of quinoa make this meal visually appealing, ensuring that it will be a hit with your family or guests.
+Whether you're serving it for a romantic dinner for two or prepping it as a meal for the week, this high-protein chicken dish is versatile and can fit seamlessly into any meal plan. 
+## Recipe Overview
+- Prep Time: 5 minutes
+- Cook Time: 15 minutes
+- Total Time: 20 minutes
+- Course: Main Course
+- Cuisine: American
+- Servings: 2
+- Calories: ~450 per serving
+## Ingredients
+- 2 boneless, skinless chicken breasts
+- 1 cup broccoli florets
+- 1 cup quinoa
+- 2 tablespoons olive oil
+- 1 teaspoon garlic powder
+- 1 teaspoon paprika
+- Salt and pepper to taste
+- 2 tablespoons lemon juice
+- Fresh parsley for garnish (optional)
+{{image_ing_1}}
+## Instructions
+1. Rinse the quinoa under cold water and cook according to package instructions.
+2. While the quinoa is cooking, heat olive oil in a large skillet over medium-high heat.
+3. Season the chicken breasts with garlic powder, paprika, salt, and pepper.
+4. Add the seasoned chicken to the skillet and cook for about 5-7 minutes on each side until fully cooked and golden brown.
+5. In the last 3 minutes of cooking the chicken, add the broccoli florets to the skillet to steam them.
+6. Once the quinoa is cooked, fluff it with a fork and drizzle with lemon juice.
+7. Slice the cooked chicken and serve it over a bed of quinoa with broccoli on the side.
+8. Garnish with fresh parsley if desired.
+## Health Benefits
+### High Protein Content
+Integrating high-protein foods like chicken and quinoa into your meals has numerous advantages. Chicken is an excellent source of lean protein, which is essential for building and repairing tissues in the body. It provides amino acids that are vital for muscle health, making it particularly beneficial for those who are physically active or engaging in regular workouts. Quinoa, often considered a superfood, not only provides a complete protein source—containing all nine essential amino acids—but also offers additional health benefits such as aiding in the regulation of blood sugar levels. This combination makes the 20-Minute High Protein Chicken Dinner ideal for sustaining energy levels throughout the day.
+### Nutrient-Rich Vegetables
+Broccoli is a powerhouse of nutrients, packed with vitamins, minerals, and antioxidants. It is an excellent source of vitamin C, which supports the immune system and promotes healthy skin. Additionally, broccoli contains vitamin K, essential for bone health and proper blood clotting. Rich in dietary fiber, it aids in digestion and contributes to a feeling of fullness, making it an essential component of a weight management plan. Moreover, phytonutrients present in broccoli have anti-inflammatory properties, contributing to overall wellness. Incorporating broccoli into this dish not only enhances its flavor but also boosts its nutritional profile significantly.
+### Healthy Fats
+Olive oil, a core ingredient used in this recipe, is celebrated for its health benefits as a source of healthy fats. It is high in monounsaturated fats, which are linked to reduced inflammation and a lower risk of heart disease. Unlike many cooking oils, olive oil has unique antioxidant properties, making it beneficial for heart health. When used for cooking, it can enhance the flavors of the ingredients while contributing to a balanced diet. Its versatility makes it a great choice for a variety of dishes, including those focusing on lean proteins and vibrant vegetables.
+## Preparation Techniques
+### Rinsing Quinoa
+Rinsing quinoa might seem like a simple step, but it plays a crucial role in the final flavor and texture of your dish. Quinoa naturally has a coating called saponin, which can impart a bitter taste if not washed away. By rinsing the quinoa under cold water before cooking, you remove this coating and reveal the delicious, nutty flavor that quinoa is known for. It's a quick step that greatly enhances the overall taste of your meal and ensures that the quinoa cooks evenly and fluffily.
+### Seasoning Chicken
+While this recipe calls for garlic powder, paprika, salt, and pepper to season the chicken, the possibilities are endless when it comes to flavoring chicken breasts. You can explore various marinades or dry rubs to suit your taste preferences. For example, consider adding herbs like thyme or oregano, or even a hint of cayenne for some heat. The key is to allow the chicken to absorb the flavors before cooking, which makes each bite deliciously savory. Properly seasoning the chicken not only enhances its flavor but also elevates the entire dish.
+### Cooking Methods for Broccoli
+When it comes to cooking broccoli, you have several options. Steaming, which is used in this recipe, helps retain the vegetable's nutrients while achieving a bright green color and tender-crisp texture. This method of cooking prevents the broccoli from becoming mushy and preserves its natural flavor. Alternatively, sautéing broccoli can also be beneficial, as it allows you to introduce additional flavors by using garlic or other aromatic ingredients. Each method affects the texture and taste, giving you flexibility in how you prepare this nutritious vegetable.
+### Troubleshooting Common Issues
+Cooking can sometimes feel intimidating, especially when it comes to managing various ingredients simultaneously. Here are some common pitfalls when preparing the components of this dish and how to avoid them:
+When using quinoa, one of the most frequent issues is undercooked grains or a mushy texture. To prevent this, always rinse the quinoa thoroughly before cooking to remove the natural coating called saponin, which can impart a bitter flavor. Make sure to follow the package instructions for water ratio, as using too much water can lead to a gummy consistency. 
+For the chicken, ensure even cooking to avoid dry pieces. If the chicken breasts are too thick, consider butterflying them to ensure uniform cooking. Using a meat thermometer can help – the chicken should reach an internal temperature of 165°F for safety and optimal juiciness. If you find that your chicken browns too quickly on the outside while remaining undercooked inside, lower the heat and extend the cooking time.
+Steaming broccoli in the skillet is convenient, but it's key to monitor it closely to avoid overcooking, which can lead to a mushy texture and loss of vibrant color. Adding the broccoli in the last few minutes of cooking the chicken allows it to become bright green and tender-crisp, retaining its nutrients and flavor.
+## Flavor Enhancements
+### Adding Spice
+While the recipe already includes garlic powder and paprika, there are a multitude of spices and herbs that can elevate the flavor profile. Adding a pinch of cayenne can bring a subtle heat to the dish, perfectly contrasting with the lemon's brightness. If you're a fan of herbs, consider incorporating dried oregano or thyme to the chicken seasoning mix. Fresh herbs such as rosemary or basil can also add an aromatic touch when sprinkled over the finished dish.
+### Citrus and Freshness
+The addition of lemon juice is not just a seasoning but a culinary game-changer. Citrus not only adds zing but enhances the flavor of the chicken and quinoa by brightening up the palates involved. Lime juice or even a splash of orange juice can be used as alternatives for a different citrus dimension. Consider zesting the lemon before juicing it; the zest adds an aromatic intensity that elevates the flavor complexity.
+### Alternative Sauces
+While the lemon juice adds freshness, you might want to explore additional sauces that can complement the dish. A drizzle of balsamic glaze can provide a sweet and tangy note, while a simple homemade sauce combining Greek yogurt with herbs can add creaminess and richness without the calories of heavier dressings. A chili oil or a sriracha-influenced sauce can also spice things up for those who enjoy a kick.
+## Serving Suggestions
+### Plating the Dish
+Presentation is key to making any meal feel special. When plating the chicken, slice it against the grain into thin strips; this enhances tenderness and visual appeal. Serve the quinoa in a bowl with a generous portion of broccoli alongside the chicken. Use a sprinkle of chopped fresh parsley to add a pop of color and freshness to the plate. For an upscale look, consider utilizing a ring mold to shape the quinoa, layering the chicken artfully on top.
+### Complementary Sides
+For a balanced meal, you might want to consider incorporating side dishes that resonate with the flavors of the main course. A simple arugula salad tossed with olive oil and a squeeze of lemon can provide a refreshing contrast. Roasted sweet potatoes or a medley of seasonal vegetables, like zucchini and bell peppers, can complement the dish beautifully while adding variety and nutrition.
+### Wine Pairing
+If you enjoy a glass of wine with your meal, this dish pairs wonderfully with a light-bodied white wine. A Sauvignon Blanc, with its citrus notes, can mirror the lemon in the dish, enhancing your overall dining experience. A Chardonnay, particularly an unoaked version, can also work well, balancing the protein and quinoa richness without dominating the palate.
+## Storage and Meal Prep
+### Leftover Storage
+To maximize the freshness and flavor of your leftovers, ensure that the Chicken Dinner is stored in an airtight container. The chicken and quinoa can last in the refrigerator for about three days. If you find yourself accumulating leftovers, it's advisable to separate the components to retain the integrity of each ingredient, particularly the broccoli which can become soggy when left in with moist foods.
+### Reheating Techniques
+When reheating the chicken and quinoa, preserve their texture by using the stovetop rather than a microwave. Gently heat in a skillet over low heat, adding a splash of water to steam the broccoli back to life. If using a microwave, cover the dish with a damp paper towel to prevent dryness. The key is to ensure the chicken reaches an internal temperature of 165°F again to maintain food safety.
+### Meal Prep Ideas
+This dish is a fantastic option for meal prepping. You can cook a double batch of quinoa and chicken during the weekend and store them in portioned containers. Prepping all ingredients ahead of time allows for quick assembly in the evenings. This not only saves time during the busy week but also supports your efforts to maintain a nutritious diet effortlessly.
+## Variations and Substitutions
+### Protein Alternatives
+While chicken is the star of this dish, there are plenty of alternatives for protein lovers. Turkey breasts can be a lean substitute, maintaining similar cooking times. For a vegetarian option, consider marinating and grilling firm tofu or tempeh; both will absorb flavors beautifully and provide a hearty protein upgrade.
+### Grain Alternatives
+If you're looking to switch up the grain, both brown rice and couscous make excellent substitutes for quinoa. Brown rice will bring a nutty flavor and chewier texture, while couscous cooks very quickly and can easily be fluffed with a fork. You may also consider farro or barley for a heartier option, adding unique flavors to the dish.
+### Vegetable Swaps
+For those who favor different vegetables, consider using asparagus, green beans, or bell peppers in place of broccoli. These veggies can be steamed or sautéed easily, aligning with the cooking method of this dish and infusing varied flavors and colors to your plate.
+## FAQs
+### How do I know when the chicken is fully cooked?
+To ensure chicken is fully cooked, rely on a meat thermometer that should read 165°F in the thickest part of the breast. Alternatively, you can cut into the chicken; the juices should run clear without any pink meat remaining.
+### Can I make this dish gluten-free?
+The beauty of this recipe lies in its naturally gluten-free ingredients. Quinoa is a fantastic gluten-free grain, making the entire dish suitable for those with gluten sensitivities or celiac disease.
+### What if I don't have olive oil?
+Olive oil can be easily substituted with other cooking oils like avocado oil or canola oil, both of which will provide a neutral flavor. Coconut oil can also work well for those who enjoy a hint of sweetness, although it may impart a slight coconut taste to the dish.
+## Conclusion
+The 20-Minute High Protein Chicken Dinner combines a rich array of textures and flavors, providing a wholesome and satisfying meal. With its quick preparation time and nutritious ingredients, this dish stands as a perfect option for anyone looking to enjoy a healthy, delectable dinner without spending hours in the kitchen. The combination of savory chicken, vibrant broccoli, and fluffy quinoa makes for a delightful dining experience.
+</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Minute High Protein Chicken Dinner</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Quick and Easy 20-Minute High Protein Chicken and Quinoa Dinner Recipe</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Quick and Healthy Chicken Quinoa Bowl</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>This quick and easy 20-minute high protein chicken and quinoa dinner is perfect for busy weeknights when you want a healthy meal without the fuss. Packed with nutritious quinoa and vibrant broccoli, this recipe ensures you enjoy a delicious, satisfying dinner that fuels your body. Try this wholesome dish for a nutritious boost that your entire family will love.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>high protein, chicken dinner, quinoa, broccoli, quick recipe, healthy meal</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Dinner</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Enjoy a quick 20-minute high protein chicken dinner. Simple, healthy, and packed with flavor – your perfect meal solution!</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_2.jpg</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/minute-high-protein-chicken-dinner/</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1521,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523214/9e559e93e93.png</t>
@@ -1136,6 +1550,176 @@
       <c r="S4" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Healthy Chicken Bowl Better Than Takeout
+## Introduction
+Exploring the world of healthy eating often leads to the discovery of vibrant, nutrition-packed recipes that are not only delicious but also satisfying. This Healthy Chicken Bowl stands out as a fantastic choice that is better than takeout. With a blend of quinoa, fresh vegetables, and perfectly cooked chicken, this dish is designed for those who want to indulge without sacrificing health.
+The beauty of this Healthy Chicken Bowl lies in its balance of flavors and textures. The nutty flavor of quinoa serves as the perfect base, while the tender, juicy chicken adds protein that keeps you full. Meanwhile, the vibrant medley of broccoli and red bell peppers provides a crunchy contrast, making each bite enjoyable. Finished off with creamy avocado slices and a drizzle of low-sodium soy sauce, this dish is not just a feast for the palate but a celebration of wholesome ingredients.
+Whether you’re dining solo or hosting a gathering, this recipe is versatile enough to serve a variety of occasions. It’s perfect for weekday dinners, meal prep, or even as a comforting dish when you need something nourishing and fulfilling. Each bowl is a wholesome meal that promises satisfaction and health in every bite.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 25 minutes
+- Total Time: 40 minutes
+- Course: Main Course
+- Cuisine: Healthy
+- Servings: 4
+- Calories: ~450 per serving
+## Ingredients
+The following ingredients are required to prepare the Healthy Chicken Bowl. Each component plays a crucial role in delivering flavor and nutrition.
+- 2 boneless, skinless chicken breasts
+- 1 cup quinoa, rinsed
+- 2 cups low-sodium chicken broth
+- 1 cup broccoli florets
+- 1 red bell pepper, diced
+- 1 avocado, sliced
+- 2 tablespoons olive oil
+- 1 tablespoon soy sauce (low sodium)
+- 1 teaspoon garlic powder
+- Salt and pepper to taste
+- Fresh cilantro for garnish (optional)
+{{image_ing_1}}
+## Instructions
+Preparing this Healthy Chicken Bowl involves a series of straightforward steps that ensure each element is cooked to perfection.
+1. In a medium saucepan, combine quinoa and chicken broth; bring to a boil, then reduce heat and simmer for 15 minutes until quinoa is fluffy.
+2. While quinoa cooks, season chicken breasts with garlic powder, salt, and pepper.
+3. Heat olive oil in a skillet over medium heat; add chicken breasts and cook for 6-7 minutes on each side until cooked through and no longer pink in the center.
+4. Remove chicken from skillet and let it rest for a few minutes, then slice into strips.
+5. In the same skillet, add broccoli and red bell pepper; sauté for 5-6 minutes until tender-crisp.
+6. In a large bowl, layer cooked quinoa, sautéed vegetables, and sliced chicken.
+7. Top with avocado slices and drizzle with soy sauce.
+8. Garnish with fresh cilantro if desired.
+### Cooking the Quinoa
+Cooking quinoa might seem daunting at first, but it's straightforward and results in a delicious and nutritious base. Begin by rinsing your quinoa under cold water to remove any excess bitterness. This step is vital because it brings out the nutty flavor of quinoa, making it even more enjoyable to eat. In a medium saucepan, combine the rinsed quinoa with low-sodium chicken broth—a perfect way to enhance the flavor without adding excessive salt.
+Bring the mixture to a boil; do not skip this part, as boiling helps to initiate the cooking process. After it reaches a boil, reduce the heat to a simmer and cover your saucepan. Simmering for 15 minutes allows the quinoa to absorb the broth, transforming it into fluffy, tender grains. Once done, remove the saucepan from the heat, but leave it covered for a few minutes to allow steam to finish the cooking process. Fluff the quinoa with a fork, and it's ready to form the base of your vibrant Healthy Chicken Bowl.
+### Preparing the Chicken
+While the quinoa is cooking, turn your attention to the chicken. Begin by seasoning the boneless, skinless chicken breasts, ensuring they are evenly coated with garlic powder, salt, and pepper. These simple seasonings not only enhance the chicken's flavor but also pair beautifully with the other ingredients in the bowl.
+Heating olive oil in a skillet brings out the richness of the chicken. Using medium heat allows for even cooking without burning the exterior while the inside remains juicy. Cook each chicken breast for about 6-7 minutes on each side. It’s essential to ensure the chicken is fully cooked and that the center is no longer pink—this ensures that you have a safe, delicious protein to enjoy. 
+After the chicken is cooked, remove it from the skillet and let it rest. Resting is crucial as it allows the juices to redistribute throughout the meat, resulting in flavorful and juicy slices. Once slightly cooled, slice the chicken into strips, ready to be layered into your bowl.
+### Vegetable Sautéing
+What’s a chicken bowl without fresh vegetables? After removing the chicken from your skillet, the residual heat and flavors left behind make for an ideal environment to sauté the vegetables. Start by adding broccoli florets and diced red bell pepper to the same skillet. Not only is this method efficient, reducing the need for additional pans, but it also infuses the veggies with the delicious garlic and chicken flavors still lingering in the pan.
+Sauté the vegetables for 5-6 minutes, stirring occasionally. Keep a close eye on them to ensure they cook through but maintain a tender-crisp texture. This means they should be vibrant in color and still offer a slight crunch when bitten into—a texture that complements the softness of the quinoa and chicken very well.
+## Assembling the Bowl
+The final step in creating your Healthy Chicken Bowl is assembly, and it’s where you can get a bit creative! Start by transferring the fluffy quinoa into a large serving bowl; this will be the foundation of your dish. 
+Next, layer in the sautéed vegetables, distributing them evenly over the quinoa. Following that, place the juicy sliced chicken on top, showcasing the vibrant colors of the red peppers and bright green broccoli. The final touch is to add the creamy avocado slices, a luscious addition that enhances the textures and flavors of the dish.
+For a drizzle of umami, lace the assembled ingredients with low-sodium soy sauce. This not only adds flavor but ties all the elements together beautifully. If you want to elevate the presentation, a sprinkle of fresh cilantro can be added for a pop of color and freshness.
+With these fundamental steps, you’ll create a healthy, visually appealing chicken bowl that rivals any takeout option, combining health, flavor, and nutrition in one perfect meal.
+nutritional value. With its vibrant ingredients and customizable nature, this dish can easily fit into various dietary preferences. Whether enjoyed as a comforting dinner or a meal prep favorite, it serves as an excellent option for those looking to maintain a healthy lifestyle.
+Scatter the sautéed vegetables over the quinoa, ensuring an even distribution of color and nutrition. The bright greens of broccoli blend beautifully with the red bell peppers, creating a visually appealing dish that whets the appetite. 
+Slice the rested chicken breasts into strips, then layer them atop the vegetable mix. The tender, juicy chicken adds substantial protein and heartiness to the bowl. When plating, consider the aesthetic: arrange the chicken strips neatly to display their golden, seared edges, which will entice anyone at the table.
+### Final Touches
+Top the bowl with creamy slices of avocado for added richness that contrasts delightfully with the savory elements of the dish. The texture of the avocado complements the crunchy veggies while contributing healthy fats, elevating the chicken bowl's overall nutrition.
+Drizzle with low-sodium soy sauce for a savory finish that enhances the flavor profile of the entire meal, tying together the diverse ingredients. The umami richness brings all components to life, making each bite a flavorful experience.
+Optionally, garnish with fresh cilantro for a burst of color and freshness. This herb adds a fragrant note that brightens the dish and balances the richness of the chicken and avocado.
+## Tips for the Perfect Chicken Bowl
+Achieving the ideal chicken bowl can be simplified with a few helpful tips. Implementing these suggestions can elevate your cooking and dining experience, making it enjoyable and manageable.
+### Choosing the Right Chicken
+Opt for high-quality, boneless, skinless chicken breasts for the best flavor and texture. Look for chicken that is pink in color without any signs of bruising or discoloration. Choosing organic or free-range options can enhance the taste and nutrition of the dish.
+### Quinoa Cooking Tips
+Rinse quinoa thoroughly before cooking to eliminate any bitterness from the outer coating, known as saponin. This step is crucial to ensure that your quinoa turns out fluffy and delicious. Cooking quinoa in low-sodium chicken broth, as noted in the recipe, enhances its overall flavor.
+### Vegetable Variations
+Feel free to customize the vegetables based on seasonality or preference; zucchini or snap peas can make excellent substitutes. The key is to choose vegetables that can be quickly sautéed while retaining some crunch, keeping the dish fresh and exciting.
+## Serving Suggestions
+This Healthy Chicken Bowl can be served in various contexts, making it a versatile dish that suits different occasions.
+### Meal Prep Options
+Prepare individual servings in advance for quick lunches or dinners throughout the week. This method not only saves time but also ensures that you have healthy, homemade food options readily available. Simply store the components separately to maintain the quality of each ingredient.
+### Pairing Ideas
+It pairs well with additional sides such as a simple green salad or a light soup. These accompaniments can complement the chicken bowl while providing further nutritional benefits, creating a well-rounded meal.
+## Storing Leftovers
+If you have any leftovers, proper storage can maintain the dish's freshness, allowing you to enjoy it again without losing flavor or texture.
+### Refrigeration Guidelines
+Store in an airtight container in the refrigerator for up to 3 days. Be sure to keep the sauce separate if possible, to prevent the quinoa from becoming mushy during storage. Properly stored, the ingredients will maintain their integrity, making reheating seamless.
+### Reheating Instructions
+Reheat gently in the microwave, ensuring the chicken stays moist. Use a microwave-safe container, cover loosely, and heat in short intervals to ensure even warming without overcooking.
+## Flavor Variations
+Exploring alternative flavors can elevate your Healthy Chicken Bowl experience. Customization not only enhances enjoyment but also allows for seasonal ingredients to shine.
+### Spice Additions
+Consider adding chili flakes or sriracha for a spicy kick that entices the taste buds. Adjust the amount to your preference; a little heat can complement the savory flavors beautifully.
+### Dressing Variants
+Experiment with a light vinaigrette or tahini-based dressing for different flavor profiles. Incorporating a tangy dressing can add an exciting twist, transforming the dish into a completely new experience while retaining its wholesome nature.
+## Health Considerations
+Understanding the nutritional aspects and suitability of the ingredients can enhance your enjoyment of the Healthy Chicken Bowl.
+### Dietary Restrictions
+This recipe caters to low-sodium diets and is gluten-free based on ingredients. Those avoiding gluten will find this bowl satisfying without compromising their dietary needs.
+### Health Benefits of Ingredients
+Each component not only contributes flavor but also delivers essential nutrients essential for a balanced diet. The combination of protein from chicken, healthy fats from avocado, and fiber from quinoa and vegetables results in a meal that supports a healthy lifestyle.
+## Conclusion
+The Healthy Chicken Bowl is a delightful main course that marries convenience with nutritional value. With its vibrant ingredients and customizable nature, this dish can easily fit into various dietary preferences. Whether enjoyed as a comforting dinner or a meal prep favorite, it serves as an excellent option for those looking to maintain a healthy lifestyle.
+</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl Better Than Takeout</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Delicious Healthy Chicken Quinoa Bowl Recipe for a Nutritious Meal at Home</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Savory Chicken Quinoa Power Bowl</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>This delicious healthy chicken quinoa bowl recipe combines the wholesome flavors of tender chicken, nutritious quinoa, and vibrant broccoli, making it a perfect meal for any season. Topped with creamy avocado, this easy dish not only satisfies your taste buds but also nourishes your body. Enjoy a nutritious meal at home that brings comfort and health to your dining table.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Healthy, Chicken, Quinoa, Avocado, Broccoli, Easy</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Enjoy a Healthy Chicken Bowl that's better than takeout! Wholesome ingredients and easy prep for a delicious meal. 🍗🥗</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_3.jpg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/healthy-chicken-bowl-better-than-takeout-8/</t>
         </is>
       </c>
     </row>
@@ -1306,6 +1890,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523165/fa5208d8215.png</t>
@@ -1334,6 +1919,167 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Quick High Protein Chicken Meal Prep
+## Introduction
+In today's fast-paced world, finding time to prepare healthy meals can be a challenge. This article explores a nutritious and easy-to-prepare meal that is perfect for health-conscious individuals looking to streamline their weekly meal prep. The Quick High Protein Chicken Meal Prep is a fulfilling dish that combines lean protein, wholesome grains, and vibrant vegetables. It not only satisfies your hunger but also nourishes your body, making it a staple in any health-focused eating plan. 
+This recipe is designed to help you save time while ensuring that you enjoy a balanced diet throughout the week. With just a few ingredients and minimal cooking time, you can set yourself up for a week of delicious meals that are easy to store and reheat. Whether you're gearing up for a busy workweek or seeking a post-workout meal, this dish stands out as an ideal option that doesn't compromise on flavor or nutrition.
+## Recipe Overview
+The Quick High Protein Chicken Meal Prep is designed to provide a balanced meal option with high protein content. This recipe is not only quick to prepare but also caters to various dietary preferences, making it a versatile addition to your meal planning repertoire.
+### Key Features
+- Healthy ingredients that promote wellness
+- High in protein, perfect for fitness enthusiasts
+- Easy to store and reheat, ideal for meal prepping
+### Nutritional Benefits
+- Chicken breasts serve as an excellent source of lean protein.
+- Quinoa is a complete protein and gluten-free grain.
+- Broccoli adds essential vitamins and minerals.
+## Ingredients
+Gathering the right ingredients is crucial for creating a delicious and nutritious meal. Here’s what you’ll need:  
+### Main Ingredients
+- **Chicken**: 1 pound boneless, skinless chicken breasts  
+- **Grains**: 1 cup quinoa, rinsed  
+- **Vegetables**: 2 cups broccoli florets  
+### Seasonings and Condiments
+- **Oil**: 1 tablespoon olive oil  
+- **Spices**: 2 teaspoons garlic powder, 1 teaspoon paprika  
+- **Flavor Enhancers**: Salt and pepper to taste, 1/4 cup low-sodium soy sauce  
+- **Optional Topping**: 1 tablespoon sesame seeds
+{{image_ing_1}}
+## Instructions
+Preparing your meal correctly sets the stage for delicious results. Follow these steps to ensure everything comes together seamlessly.  
+1. Preheat the oven to 400°F (200°C).  
+2. In a bowl, mix olive oil, garlic powder, paprika, salt, and pepper. Coat the chicken breasts in the mixture.  
+3. Place the chicken on a baking sheet and bake for 20-25 minutes or until fully cooked.  
+4. While the chicken is baking, cook quinoa according to package instructions.  
+5. Steam the broccoli florets until tender, about 5-7 minutes.  
+6. Once the chicken is cooked, let it rest for 5 minutes before slicing it into strips.  
+7. Divide the quinoa, broccoli, and chicken into meal prep containers.  
+8. Drizzle with soy sauce and sprinkle sesame seeds on top if using.  
+9. Allow to cool before sealing containers and refrigerating.  
+10. Enjoy your high-protein meal throughout the week!  
+## Assembling the Meal Prep
+Once all components are cooked, it's time to assemble your meal prep containers. Begin by preparing your workspace and ensuring that all necessary containers are clean and ready for use. It's essential to have a structured approach when dividing your meals, as this will optimize your meal prep experience. 
+### Slicing the Chicken
+After baking, it is crucial to give the chicken some time to rest. This resting period, about five minutes, allows the juices to redistribute, ensuring that each slice remains moist and flavorful. Once rested, slice the chicken into strips for easy portioning. These strips will nestle perfectly alongside the quinoa and broccoli, creating a balanced plate that not only looks appealing but tastes fantastic as well.
+### Portioning the Ingredients
+Now, take your meal prep containers and begin adding the quinoa. A scoop of perfectly cooked quinoa should fill the base of each container. Follow this by placing an equal portion of steamed broccoli florets next to the quinoa, creating a colorful and nutritious base for your meal. Finally, position the sliced chicken strips on top. This method of layering ensures that each meal is not only visually appealing but also balanced in terms of nutritional content.
+### Final Touches
+Once each component has been added to your containers, it’s time for those final touches that elevate the dish. Drizzle a modest amount of low-sodium soy sauce over the chicken and veggies to introduce an umami flavor, enhancing the overall taste of the meal. If you're a fan of added crunch and further flavor, feel free to sprinkle sesame seeds over the top. While this ingredient is optional, it certainly adds a delightful texture and nuttiness that perfectly complements the other flavors.
+As you complete the assembly of each container, allow them to cool slightly. It is important to let the meals reach a temperature that is not too hot before sealing them. This practice helps maintain the quality of your meal prep through the week and allows for safe storage in the refrigerator. Once cooled, you can securely seal your containers, placing them in the fridge for easy access during your hectic week.
+### Enjoying Your Meals
+The Quick High Protein Chicken Meal Prep allows you to enjoy nutritious meals any day of the week without spending hours in the kitchen each evening. By preparing these containers in advance, you’ll save time and create a set of meals that provide balanced nutrition. This dish is excellent served cold straight from the fridge or reheated in the microwave, making it a versatile choice for lunch or dinner. Whether you're heading to work, hitting the gym, or spending a day at home, these meals are designed to nourish and satisfy, keeping you energized and ready for whatever lies ahead.
+### Portioning the Ingredients
+Dividing the cooked quinoa, steamed broccoli, and chicken strips into meal prep containers is a crucial step in the meal prep process. This ensures each serving is balanced and nutritious, contributing to a well-rounded diet that supports your healthy lifestyle. With a recipe designed to serve four, careful portioning allows you to manage your daily intake effectively while also making sure that you have enough for your weekly meal plan.
+Begin by adding an equal amount of quinoa to each container. This grain is not only a great source of fiber but also provides a healthy dose of protein, making it a worthy addition to any meal. Next, layer the broccoli florets evenly amongst the containers. The vibrant green color offers not just visual appeal but also a wealth of vitamins and minerals, elevating the nutritional value of your meal prep. Finally, place the sliced chicken strips on top. Arranging the components in this manner enhances the meal’s presentation, making it more enjoyable to eat.
+### Adding Flavor
+To take these meals from good to great, adding flavor is essential. Drizzling the prepared meal with low-sodium soy sauce is a simple yet effective method for enhancing the overall taste. This ingredient adds a savory depth that complements the chicken, quinoa, and broccoli beautifully. The low-sodium variant is recommended to maintain a healthy sodium intake while still enjoying the rich flavor that soy sauce offers.
+For an additional touch, consider sprinkling sesame seeds on top. This optional ingredient not only adds a delightful crunch but also visual appeal, making your meal prep containers vibrant and enticing. Sesame seeds are nutrient-dense and, when toasted, can release a nuttiness that further enriches the flavor profile of your meals. 
+## Cooling and Storing
+Proper cooling and storage are essential for maintaining freshness in your meal prep. Addressing these aspects will ensure that your meal remains safe to eat and delicious throughout the week.
+### Cooling the Meal Prep
+Once you have filled your meal prep containers, it’s important to allow them to cool down before sealing. This step is vital as it helps prevent condensation, which can result in soggy meals and spoilage. By letting the meal cool to room temperature, you maintain the integrity of the ingredients and ensure that your meals taste fresh when reheated later. Typically, allowing the meals to sit for about 20-30 minutes should be sufficient.
+### Storing in the Refrigerator
+After cooling, seal the containers tightly to maintain freshness. Store them in the refrigerator where they can be kept for up to a week. This makes the Quick High Protein Chicken Meal Prep a fantastic option for busy individuals looking to eat healthy throughout the week. By having these meals readily available, you can easily grab one on your way out or heat it up for lunch, eliminating the temptation to opt for less healthy choices.
+## Serving Suggestions
+Exploring different ways to enjoy the Quick High Protein Chicken Meal Prep can add excitement to your daily meals and help you avoid mealtime monotony.
+### Pairing Ideas
+To enhance the meal's nutritional value and flavor, consider serving it with a side salad. A mix of greens, colorful vegetables, and a light vinaigrette can provide essential nutrients and fiber, complementing your chicken and quinoa. Additionally, pairing your meal with a healthy dip like hummus or tzatziki can offer contrasting flavors and textures, making the eating experience more enjoyable. These pairings not only expand the meal’s flavor profile but also promote a more varied diet which is beneficial for overall health.
+### Reheating Options
+When it comes time to eat, reheating options are important for maintaining the quality of your meal. The quickest method is to use a microwave; simply cover the container and heat until the food is warmed through. Be cautious not to overheat, as this can dry out the chicken. Alternatively, for those who prefer their meals evenly warmed, reheating the chicken and quinoa in the oven is a great option. Set your oven to a low temperature, and for best results, cover the dish with foil to retain moisture while heating.
+## Variations and Adaptations
+One of the great things about meal prep is how easily it can be customized based on dietary preferences or ingredient availability.
+### Protein Alternatives
+If you’re looking for a vegetarian version of this meal prep, substituting chicken with tofu or tempeh is an excellent option. Both provide a hearty texture and can absorb flavors from your seasoning mix, making them just as delicious. For seafood lovers, shrimp is a fantastic alternative that cooks quickly and offers a different flavor profile. Additionally, turkey can be utilized for a leaner protein option that can be seasoned similarly to chicken.
+### Grain Options
+To keep things interesting, consider swapping out quinoa for other grains like brown rice, farro, or bulgur. These options can offer varied textures and nutritional benefits. Farro, for instance, is a great source of fiber and protein, while brown rice provides complex carbohydrates. Experimenting with different cooking methods—such as boiling or pressure cooking—can also yield varied textures, making your meals even more appealing.
+## Storing for Freshness
+Implementing best practices for storage ensures that your meal prep remains fresh for as long as possible, allowing you to stick to your healthy eating goals.
+### Container Choices
+Choosing the right containers is essential for safe storage. Opt for BPA-free containers to ensure that your food is kept free from harmful chemicals. Glass containers are highly recommended as they are durable, do not retain odors, and can maintain heat efficiently. This makes them ideal for both storage and reheating.
+### Monitoring Shelf Life
+Regularly checking your meals for freshness is key to making the most of your meal prep. Consume the oldest meals first to prevent waste. Labeling containers with the dates they were prepared is a practical method for tracking storage duration and ensuring you enjoy your meals at their best.
+## Nutritional Considerations
+Understanding the nutritional value of your meals can enhance your meal planning and assist in achieving health goals.
+### Caloric Information
+With approximately 400 calories per serving, this meal prep offers a balanced and nourishing option that aligns well with many dietary needs. The combination of protein, healthy fats, and carbohydrates not only supports energy levels throughout the day but also promotes satiety, helping you feel full and satisfied.
+In conclusion, the Quick High Protein Chicken Meal Prep is a versatile, nutritious, and easy-to-prepare option that fits seamlessly into a busy lifestyle. By following proper storage and reheating techniques, as well as considering adaptations and pairings, you can enjoy delicious, healthy meals throughout the week while keeping your taste buds engaged.
+</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Quick High Protein Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Meal Prep with Quinoa and Broccoli</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Savory Chicken Quinoa Bowl</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Discover this easy high protein chicken meal prep recipe featuring quinoa and broccoli, perfect for busy weeknights. Packed with nutrients and flavor, this healthy cooking option simplifies your meal planning while keeping you energized and satisfied. Enjoy the delicious combination of tender chicken, wholesome quinoa, and vibrant broccoli as you nourish your body with each bite.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>high protein, meal prep, chicken recipe, quinoa, healthy cooking, broccoli</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Prepare delicious high-protein chicken meal prep in just 40 minutes! Perfect for your healthy weekly meal plan.</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_4.jpg</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/quick-high-protein-chicken-meal-prep/</t>
         </is>
       </c>
     </row>
@@ -1508,6 +2254,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523173/a7ab30c3539.png</t>
@@ -1536,6 +2283,167 @@
       <c r="S6" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy Chicken and Rice High Protein Recipe
+## Introduction
+The Easy Chicken and Rice High Protein Recipe is a simple yet satisfying dish that has quickly become a staple in many households. Combining tender chicken breast with nutritious brown rice and vibrant broccoli, this recipe stands out for its ability to deliver both flavor and nutrition in one delightful meal. The rich aroma of spices mingling with sautéed onions and garlic creates an inviting atmosphere in your kitchen, making it an ideal choice for gatherings and family dinners. 
+As busy schedules often leave little time for extensive cooking, this recipe shines by providing a wholesome and hearty meal in just over forty minutes. It suits various occasions, whether you're preparing a quick weeknight dinner or meal-prepping for the week ahead. Healthy and filling, this dish makes sure you remain satisfied without compromising on taste.
+## Recipe Overview
+- Prep Time: 10 minutes  
+- Cook Time: 40 minutes  
+- Total Time: 50 minutes  
+- Course: Main Course  
+- Cuisine: American  
+- Servings: 4  
+- Calories: ~450 per serving  
+## Ingredients
+The following ingredients are required to prepare the Easy Chicken and Rice dish:  
+- 1 lb boneless, skinless chicken breast, diced  
+- 1 cup brown rice  
+- 2 cups low-sodium chicken broth  
+- 1 cup broccoli florets  
+- 1 medium onion, chopped  
+- 2 cloves garlic, minced  
+- 1 teaspoon paprika  
+- 1 teaspoon black pepper  
+- 1 tablespoon olive oil  
+- Salt to taste
+{{image_ing_1}}
+## Preparation Tips
+### Selecting Ingredients
+Choosing high-quality chicken breast and fresh vegetables can significantly enhance the overall flavor of the dish. Opt for chicken breasts that are firm with no discoloration. Fresh broccoli will not only contribute vibrant color but also essential nutrients to your meal. If possible, select organic ingredients to avoid pesticides and ensure better taste.
+### Cooking Equipment
+A large skillet is essential for this recipe as it allows for properly sautéing the ingredients while facilitating even cooking. A skillet with a lid is ideal for the simmering step, ensuring that the rice cooks evenly and retains moisture for a fluffy texture.
+### Prepping Ahead
+Pre-dicing the chicken and chopping the vegetables can cut down on your prep time significantly. This preparation can be done the day before and stored in separate containers in the refrigerator, making it easy to get started when you're ready to cook. Having your ingredients prepped ensures that you can quickly move through the cooking process without unnecessary delays. 
+## Step-by-Step Cooking Instructions
+### Sautéing the Aromatics
+To kick things off, begin by heating the olive oil over medium heat in a large skillet. Once the oil is hot, add the chopped onion and minced garlic, cooking them until the onion becomes translucent. This initial step is crucial as it provides a flavorful base for your dish. The caramelization of the onion and the fragrance of garlic will elevate the entire meal's aroma. 
+### Cooking the Chicken
+After achieving the right texture with your aromatics, it’s time to add the diced chicken breast to the skillet. Cook the chicken, ensuring it browns evenly on all sides, which should take about 5-7 minutes. Browning not only enhances the flavor profile through the Maillard reaction but also seals in the juices, making the chicken tender and juicy. Stir occasionally to prevent sticking and ensure even cooking.
+### Adding Seasoning
+Next, you’ll want to enhance the flavor of the chicken mixture. Sprinkle in the paprika, black pepper, and salt. Stir well to ensure that each piece of chicken is well-coated with the spices. The paprika adds a warm, smoky flavor, while the black pepper adds a kick, making this dish full of savory depth. The salt is essential for bringing out the natural flavors of all the ingredients.
+## Cooking the Rice
+### Incorporating the Rice
+Once the chicken is well-seasoned and cooked, proceed by adding the brown rice to the skillet. Stir the rice thoroughly to combine it with the chicken and spices, allowing it to absorb all those delicious flavors. This step is key, as it ensures the rice becomes an integral part of the dish rather than just a side.
+### Simmering
+Now it’s time to add the chicken broth. Pour in 2 cups of low-sodium chicken broth and bring the mixture to a boil. Once it reaches a vigorous boil, reduce the heat to low, cover the skillet, and let it simmer for 30 minutes. This slow-cooking method allows the rice to absorb the broth, plumping it up and making it fluffy, while the chicken continues to infuse its flavor throughout.
+## Adding Vegetables
+After the initial 30 minutes of simmering, it’s time to incorporate the broccoli florets. Place them on top of the rice mixture in the skillet, cover again, and cook for an additional 5-10 minutes. The steam created within the skillet during this time will perfectly cook the broccoli, ensuring it remains vibrant and rich in nutrients, while also retaining a crisp texture that contrasts nicely with the tender chicken and rice. 
+This method of adding vegetables at the end not only keeps them distinct and flavorful but also highlights their naturally vivid colors, making for an appealing presentation on your dinner table. As the broccoli cooks, keep an eye on the mixture to determine when it reaches your preferred tenderness. 
+In the next segment, we’ll continue with the final steps of the cooking process, which include fluffing the rice and serving the dish to family and friends. Stay tuned for tips on presentation and garnishing that will elevate your dining experience!
+### Timing the Broccoli
+After allowing the rice to simmer adequately, it's time to incorporate the broccoli. Carefully place the fresh broccoli florets on top of the rice mixture. It's essential to do this without stirring, preserving the layers that will ensure even cooking. Once the florets are positioned, re-cover the skillet to trap steam and heat, which will help cook the broccoli evenly.
+### Finishing Cooking
+Cook the covered dish for an additional 5-10 minutes. This step is crucial, as it allows the broccoli to soak up the flavors from the chicken broth and spices while simultaneously softening. You'll notice the vibrant green of the broccoli brightening, enhancing the dish's appeal. Monitoring the broccoli closely is key; it should be tender but still have a slight crunch to it for the best texture.
+## Resting and Fluffing
+### Letting it Sit
+Once the cooking time is complete, remove the skillet from the heat. Allow it to sit for about 5 minutes while still covered. This resting period is vital as it lets the flavors meld beautifully, resulting in a more savory dish. The rice will also absorb any remaining moisture during this time, enhancing the overall texture and preventing the dish from becoming too soggy.
+### Fluffing the Rice
+After the resting period, use a fork to gently fluff the rice. This technique helps to separate the grains, preventing clumps and ensuring an airy texture. As you fluff the rice, the chicken and broccoli will intermingle, spreading the flavors throughout the dish. This step not only improves presentation but also makes each bite deliciously balanced with chicken, rice, and vegetables.
+## Serving Suggestions
+### Plating the Dish
+When serving, consider how to create an inviting presentation. Use a large spoon to scoop portions of the chicken and rice mixture onto plates, ensuring that each serving gets a healthy portion of broccoli as well. The contrasting colors of the brown rice, golden chicken, and bright green broccoli create an eye-catching dish. For an added touch, you might serve it next to a side salad or with crusty bread to provide some variety.
+### Garnishing Options
+To elevate the dish further, you can sprinkle fresh herbs on top before serving. Chopped parsley, cilantro, or even basil can add color and a burst of fresh flavor to the hearty meal. A hint of freshly cracked black pepper on top can also enhance the dish's visuals and taste, making it even more appealing to the eye and palate.
+## Nutritional Information
+### Understanding the Calories
+Each serving of this Easy Chicken and Rice dish contains approximately 450 calories. This makes it a well-rounded meal option for individuals looking to maintain a healthy diet without compromising on flavor or satisfaction. The calorie count is particularly beneficial for those who are mindful of their intake but still want a fulfilling meal.
+### Protein-Rich Profile
+The combination of chicken breast and brown rice presents a notable protein-rich profile. Chicken breast is renowned for being a lean source of protein, essential for muscle repair and growth. Coupled with brown rice, which offers fiber and additional nutrients, this dish is ideal for anyone needing sustained energy, making it a prime choice for athletes or active individuals.
+## Variations &amp; Substitutions
+### Protein Alternatives
+If you're looking to diversify the protein source in this recipe, consider substituting the chicken breast with turkey or tofu. Turkey is another lean meat option that holds flavor well and aligns with the healthy profile of the original recipe. Tofu provides a plant-based alternative that absorbs surrounding flavors beautifully. The cooking process remains largely the same, ensuring a delicious outcome regardless of your choice.
+### Vegetable Options
+To enhance the nutritional value and aesthetic of your dish, feel free to add other vegetables. Bell peppers add a sweet crunch, while spinach can bring about a delightful touch of earthiness. You could even consider adding peas or green beans for variety. As with the broccoli, these vegetables should be added towards the end of the cooking time to prevent overcooking, maintaining their vibrant color and nutrients.
+## Common Mistakes to Avoid
+### Overcooking the Chicken
+One prevalent mistake to watch for while preparing this dish is overcooking the chicken. Keeping an eye on the cooking time is essential; cooking it just until it is browned and cooked through will lead to tender, juicy pieces rather than dry, tough ones. Cooking to the proper internal temperature should be your guide; chicken is perfectly cooked at 165°F.
+### Cooking Rice Incorrectly
+Another common oversight is not rinsing the rice before cooking. Rinsing brown rice helps remove excess starch, which can lead to a gummy texture if not properly addressed. A simple rinse under cool water a few minutes before cooking can transform the dish and ensure each grain is separate and fluffy.
+## Storing Leftovers
+### Refrigeration Tips
+Should you have any leftovers, storing them properly is crucial. Place the remaining chicken and rice mixture in an airtight container, and refrigerate. This will not only preserve freshness but also maintain the flavors. The dish can be safely stored in the fridge for up to 3 days.
+### Reheating Methods
+When it’s time to enjoy your leftovers, reheat them gently in the microwave or on the stovetop. If the mixture appears dry, adding a splash of chicken broth can restore the moisture, keeping the dish delicious and satisfying. Stir well during reheating to ensure even heating throughout, maintaining the integrity of the chicken and broccoli.
+## Conclusion
+The Easy Chicken and Rice High Protein Recipe is a delightful combination of flavors and textures, delivering a wholesome meal in just 50 minutes. This dish offers an impressive balance of hearty chicken, nutritious rice, and fresh broccoli, making it a comforting and family-friendly option. Its rich protein content aligns well with an active lifestyle, ensuring it remains a staple on dinner tables.
+</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Easy Chicken and Rice High Protein Recipe</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Easy High-Protein Chicken and Rice Recipe with Broccoli and Garlic</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Savory One-Pan Chicken and Rice</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Elevate your mealtime with this easy high-protein chicken and rice recipe featuring fresh broccoli and garlic. Perfect for a healthy weeknight dinner, this nutritious dish is not only simple to prepare but also satisfying and full of flavor. Enjoy a wholesome meal that brings comfort and health to your table any time of year.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>chicken, rice, high protein, healthy recipe, easy meal, broccoli</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Easy Chicken and Rice Recipe</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Enjoy this Easy Chicken and Rice high protein recipe, packed with flavor and perfect for a healthy meal! 🍗🍚</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_5.jpg</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/easy-chicken-and-rice-high-protein-recipe/</t>
         </is>
       </c>
     </row>
@@ -1704,6 +2612,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523160/8dfe5ba75e1.png</t>
@@ -1732,6 +2641,164 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># High Protein Chicken Wrap for Busy Days
+## Introduction
+The high protein chicken wrap is the perfect solution for busy individuals seeking a nutritious and filling meal. Packed with protein from chicken and Greek yogurt, and loaded with fresh vegetables, this wrap is a great choice for lunch. Whether you’re rushing between meetings, heading to the gym, or simply want a quick meal, this recipe is easy to prepare in just ten minutes and is deliciously satisfying.
+This wrap not only delivers an impressive protein punch but also brings together a symphony of flavors and textures. From the creamy Greek yogurt to the crisp cucumbers and vibrant spinach, each bite is a celebration of health and convenience. With no cooking required, you can throw this together even on the busiest of days, making it an ideal option for a nutritious packed lunch or a quick post-workout meal.
+The balance of ingredients in this chicken wrap provides a wholesome and balanced meal. It’s an excellent way to indulge in a filling dish that doesn’t compromise on health. Its simplicity makes it easy to customize, allowing you to add your favorite flavors or extra crunch. It's flavor, nutrition, and convenience rolled into one, making it a standout choice for anyone needing to fuel their day effectively.
+## Recipe Overview
+- Prep Time: 10 minutes  
+- Cook Time: 0 minutes  
+- Total Time: 10 minutes  
+- Course: Lunch  
+- Cuisine: American  
+- Servings: 1  
+- Calories: ~450 per serving  
+## Ingredients
+- 1 large whole wheat tortilla
+- 4 oz cooked chicken breast, shredded
+- 1/2 cup Greek yogurt
+- 1/4 cup diced cucumbers
+- 1/4 cup chopped tomatoes
+- 1/4 avocado, sliced
+- 1 cup spinach leaves
+- Salt and pepper to taste
+- Optional: hot sauce or your favorite dressing
+{{image_ing_1}}
+## Instructions
+1. Lay the whole wheat tortilla flat on a clean surface.
+2. Spread the Greek yogurt evenly over the tortilla, leaving a small border around the edges.
+3. Layer the shredded chicken breast on top of the yogurt.
+4. Add the diced cucumbers, chopped tomatoes, and spinach leaves evenly over the chicken.
+5. Place the avocado slices on top and season with salt and pepper.
+6. If desired, drizzle with hot sauce or your favorite dressing for extra flavor.
+7. Carefully fold in the sides of the tortilla, then roll it up tightly from the bottom to the top.
+8. Slice the wrap in half diagonally for easy eating.
+9. Wrap in foil or parchment paper for a convenient grab-and-go option.
+## Preparation Method
+### Laying the Foundation
+To begin your high protein chicken wrap, start by laying the whole wheat tortilla flat on a clean surface. Choosing the right surface is essential; a smooth, sturdy cutting board or clean countertop works best. Once the tortilla is in position, it’s important to spread the fillings evenly. Leaving a small border around the edges will help prevent any spillage when you roll it up, ensuring a neat and appealing wrap that retains its shape.
+### Spreading the Base
+Next, take the Greek yogurt and spread it evenly across the tortilla. The yogurt serves as a deliciously creamy base, adding moisture and flavor. Aim for an even thickness, but you won’t need to overdo it; too much could cause the wrap to become soggy. Use a spatula or the back of a spoon for even distribution, ensuring that every bite will carry that tangy flavor.
+### Layering Ingredients
+After your yogurt base is prepared, the next step involves layering the ingredients. Start with the shredded chicken breast, placing it on top of the Greek yogurt. This not only keeps the chicken direct contact with the moisture of the yogurt but also creates a wonderful texture contrast within the wrap. Following the chicken, add the diced cucumbers, chopped tomatoes, and spinach leaves. The cucumbers add crunch and hydration, while the tomatoes introduce a burst of freshness, with the spinach enriching your wrap with additional vitamins and minerals. Finally, top everything off with slices of avocado to provide healthy fats, which also enhance the overall flavor profile.
+### Seasoning the Wrap
+Once all the ingredients are layered beautifully, it’s time to season your wrap. Simple salt and pepper will elevate the overall flavor of the ingredients. Season according to taste; a couple of pinches should suffice for this slightly creamy and fresh mix. If you're looking for added kick, consider drizzling with hot sauce or your favorite dressing. This step allows for a personal touch, letting you adapt the wrap to your specific flavor preferences.
+### Rolling the Wrap
+Careful rolling is key to achieving a well-formed wrap. Begin by folding in the sides of the tortilla—this prevents the fillings from falling out. Next, roll it up tightly from the bottom to the top, ensuring that everything stays inside. The technique here is crucial; a snug roll will keep your ingredients tightly packed. Once rolled, slice the wrap in half diagonally for optimal presentation and ease of eating. This not only makes for a visually appealing dish but also provides an easy grip for each bite. 
+After slicing, feel free to wrap your high protein chicken wrap in foil or parchment paper. This not only keeps it fresh but also allows for zipping it into a bag for an easy grab-and-go option. Perfect for those on the run, this wrap can be consumed anytime and anywhere, making it a favorite for busy days.
+## Nutritional Benefits
+### High Protein Content
+One of the standout features of this recipe is its high protein content, primarily sourced from the cooked chicken breast and Greek yogurt. Chicken breast is well-known for being lean, packing in protein necessary for muscle repair and growth, especially beneficial after workouts. Coupled with Greek yogurt, which is also rich in protein, this wrap sets a solid foundation for muscle recovery while offering a delightful texture that makes every bite pleasurable. This combination does not just satiate your hunger but also fuels your body in a healthy way, making it an excellent choice for those mindful of their nutritional intake. 
+When you combine such high-protein ingredients with fiber-rich whole wheat tortillas and fresh vegetables, the nutritional benefits multiply, creating a meal that is both filling and supportive of a healthy lifestyle. The emergence of this wrap as a go-to lunch option is no surprise, given its health-conscious characteristics and easy prep.
+### The importance of protein in a balanced diet, particularly for active individuals
+Protein plays a crucial role in maintaining muscle mass, repairing tissues, and supporting overall health, especially for those engaged in fitness activities or strenuous lifestyles. Consuming an adequate amount of protein aids in muscle recovery and performance, making it essential for active individuals. The chicken in the high protein chicken wrap serves as an excellent source of lean protein, providing necessary amino acids that the body requires for rebuilding and recovery. Additionally, incorporating protein-rich foods into meals can help boost satiety, which may prevent overeating during the day and support weight management.
+### Wholesome Ingredients
+### Health benefits of whole wheat tortillas versus white flour alternatives
+Whole wheat tortillas are a healthier choice compared to traditional white flour tortillas due to their higher fiber content. Fiber is essential for digestive health, promoting a feeling of fullness, and helping to regulate blood sugar levels. Whole grains have also been associated with a reduced risk of chronic diseases such as heart disease and diabetes. This wrap utilizes a large whole wheat tortilla, enhancing its nutritional value and providing a robust base for the other ingredients.
+### Benefits of fresh vegetables—vitamins, minerals, and antioxidants
+The inclusion of fresh vegetables like cucumbers, tomatoes, spinach, and avocado brings a plethora of vitamins, minerals, and antioxidants to the chicken wrap. Cucumbers are hydrating and low in calories, while tomatoes provide vitamin C, potassium, and lycopene—an antioxidant linked to reduced risk of certain cancers. Spinach is rich in iron, magnesium, and numerous vitamins, contributing to bone health and energy levels. Lastly, avocados offer potassium and are loaded with healthy fats that benefit heart health. Together, these vegetables not only enhance flavor and texture but also significantly boost the overall nutritional profile of the meal.
+### Healthy Fats
+### The significance of incorporating avocado and its heart-healthy properties
+Avocado is a powerhouse of healthy monounsaturated fats, which are known to support heart health by lowering bad cholesterol levels. The creamy texture and mild flavor of avocado help create a balanced wrap, contributing to its deliciousness while providing essential fatty acids. These fats are vital for the absorption of fat-soluble vitamins (A, D, E, and K) and play a key role in inflammation reduction. The presence of avocado in this dish is an excellent way to incorporate nourishing fats into your diet.
+### How healthy fats contribute to overall satiety and flavor profile
+Healthy fats, like those found in avocados, contribute to a satisfying meal. They help the body feel full longer and stabilize blood sugar levels, making it easier to maintain energy throughout the day. Incorporating these fats into the high protein chicken wrap not only enhances its flavor but also makes the meal more enjoyable, aligning with nutritional needs and dietary goals.
+## Meal Prep Tips
+### Preparing Ahead of Time
+For busy days when time is limited, preparing ingredients in advance can make assembly quick and easy. Shredding chicken in advance and storing it in an airtight container ensures it’s ready to add to the wrap. This not only cuts down on preparation time but allows you to enjoy a nutritious meal without significant effort. You can also pre-chop vegetables, separating them into containers for easy access. Having everything ready to go streamlines the process of creating your chicken wrap when hunger strikes.
+### Storage Guidelines
+If you’re making the wrap ahead of time, proper storage ensures maximum freshness. It's best to wrap the completed chicken wrap in foil or parchment paper, which prevents it from becoming soggy and maintains its structure. Ideally, aim to consume the wrap within a day for the best taste and texture. If you prefer, you can also store ingredients separately for a build-your-own wrap experience, preserving the freshness of each component until you're ready to enjoy your meal.
+## Variations and Substitutions
+### Protein Swaps
+For those looking to modify the protein source, there are numerous options available. Turkey is a lean alternative that maintains a similar taste and texture while slightly altering the nutrient profile. Tofu is an excellent plant-based protein that absorbs flavors well, making it a versatile swap, especially for vegetarian diets. Chickpeas are another great substitution for those seeking a hearty protein source that increases dietary fiber content. Each of these protein options has unique benefits while still maintaining the essence of the wrap.
+### Vegetable Alternatives
+If you wish to diversify your vegetable options, consider using bell peppers, carrots, or even arugula. Bell peppers add sweetness and a crunch that contrasts nicely with the creamy avocado, while carrots offer a satisfying crispness and additional vitamin A. Arugula brings a peppery bite, complementing the flavors of the chicken and yogurt beautifully. These variations give the wrap new textures and tastes while keeping it healthy and delicious.
+### Dressing Ideas
+The right dressing can significantly enhance the flavor of your wrap. Options like hot sauce or vinaigrettes can contribute tanginess and a bit of spice. Homemade dressings, such as a simple lemon-tahini sauce or a yogurt-based ranch, can elevate the flavor while maintaining health benefits. Experimenting with different sauces not only adds variety but can also help you discover new favorite combinations.
+## Serving Suggestions
+### Enjoying the Wrap Solo
+This high protein chicken wrap stands alone as a complete meal, making it ideal for busy weekday lunches or on-the-go snacks. Its combination of protein, healthy fats, and fresh vegetables provides balanced nutrition within a simple, handheld package. The wrap has a delightful flavor profile, from the rich chicken to the refreshing crunch of cucumbers and the creaminess of avocado, creating a satisfying and healthful dining experience.
+### Pairing with Sides
+For those wanting a more rounded meal, consider pairing the wrap with healthy side dishes like a fresh fruit salad or crunchy veggie sticks. These sides not only complement the wrap’s flavors but enhance the overall nutritional balance of the meal. Additionally, drinks like herbal teas or infused water offer refreshing options that harmonize with the wrap without adding unnecessary sugars.
+## Conclusion
+This high protein chicken wrap offers a delightful blend of flavor and nutrition within a short preparation time of just ten minutes. With its satisfying textures and vibrant ingredients, it serves as a wholesome lunch option perfect for anyone on the go. Enjoy the convenience and health benefits while indulging in this tasty wrap.
+</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Wrap for Busy Days</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Wrap Recipe for Quick Lunches</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Quick and Healthy Chicken Wrap</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Discover an easy high-protein chicken wrap recipe that’s perfect for quick lunches on busy days. Packed with flavorful grilled chicken, fresh veggies, and creamy Greek yogurt, all wrapped in a wholesome whole wheat tortilla, this healthy lunch option will keep you satisfied and energized. Enjoy this nutritious recipe as a convenient meal that fuels your day.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>high protein, chicken wrap, whole wheat tortilla, Greek yogurt, healthy lunch, quick recipe</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Wrap</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Enjoy a quick and healthy high protein chicken wrap packed with flavor, perfect for busy days on the go! 🌯💪</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_6.jpg</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/high-protein-chicken-wrap-for-busy-days/</t>
         </is>
       </c>
     </row>
@@ -1898,6 +2965,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523161/e3e3f71c145.png</t>
@@ -1928,6 +2996,173 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Simple Chicken Bowl for Weight Loss
+## Introduction
+In today’s fast-paced world, healthy eating can often seem like a daunting task. However, preparing balanced meals is essential not just for maintaining a healthy weight but also for fueling our bodies with the nutrients they need. A healthy diet helps boost energy levels, improves mental focus, and supports overall well-being. By choosing wholesome ingredients that are rich in flavor and beneficial nutrients, we pave the way for a sustainable lifestyle change.
+The Simple Chicken Bowl is an excellent example of how to create a meal that is both delicious and nutritious. Perfect for those seeking to lose weight without sacrificing taste, this bowl is loaded with protein, healthy fats, and fiber. Whether you're meal prepping for the week or looking for a quick and easy dinner option, this chicken bowl is versatile enough to be enjoyed at any time of the day. With its colorful ingredients and satisfying flavors, it makes healthy eating delightfully simple and appealing.
+## Recipe Overview
+- Prep Time: 10 minutes  
+- Cook Time: 15 minutes  
+- Total Time: 25 minutes  
+- Course: Main Course  
+- Cuisine: Healthy  
+- Servings: 2  
+- Calories: ~450 per serving  
+The Simple Chicken Bowl is a wholesome dish that brings together various ingredients to create a balanced meal. Each component offers unique health benefits that contribute to your overall dietary goals, particularly for weight loss. This dish is not only easy to prepare but also explodes with flavor, thanks to the blend of fresh vegetables and a zesty dressing of olive oil and lemon juice. 
+With its protein-packed grilled chicken and fiber-rich quinoa, this bowl caters to your hunger while ensuring you receive essential nutrients. The addition of vibrant steamed broccoli and juicy cherry tomatoes enhances both the nutrition and the visual appeal. It's a meal that can be tailored to your preferences, making it ideal for anyone looking to enjoy their food while still focusing on healthy eating.
+## Ingredients
+- 1 cup cooked quinoa  
+- 4 oz grilled chicken breast, sliced  
+- 1/2 cup steamed broccoli  
+- 1/2 cup cherry tomatoes, halved  
+- 1/4 avocado, sliced  
+- 1 tablespoon olive oil  
+- 1 tablespoon lemon juice  
+- Salt and pepper to taste  
+- Fresh parsley for garnish  
+Each ingredient in this bowl not only enhances the overall flavor but also contributes significantly to your nutritional intake. Quinoa, known for being a complete protein, combines all the essential amino acids, which makes it a perfect choice for those looking to maintain muscle mass while losing weight. Alongside quinoa, grilled chicken serves as a lean protein source, crucial for recovery and building muscle.
+Adding steamed broccoli boosts the fiber content while supplying a myriad of vitamins and minerals essential for optimal health. The vibrant cherry tomatoes, rich in antioxidants, bring a refreshing sweetness to the mix. Avocado enriches the dish with healthy fats and vital vitamins, making you feel satiated. Olive oil serves as a heart-healthy fat that enhances both flavor and nutrient absorption, while lemon juice provides a zesty freshness along with vitamin C. A sprinkle of salt and pepper allows you to customize the flavor, while fresh parsley adds a touch of elegance and herbal notes.
+{{image_ing_1}}
+## Instructions
+1. Cook the quinoa according to package instructions and set aside to cool.
+2. Grill or pan-sear the chicken breast until fully cooked, then slice it into strips.
+3. Steam the broccoli until tender, about 4-5 minutes.
+4. In a large bowl, combine the cooked quinoa, grilled chicken, steamed broccoli, and cherry tomatoes.
+5. Drizzle the olive oil and lemon juice over the mixture, then season with salt and pepper.
+6. Gently toss all ingredients together until well mixed.
+7. Top the bowl with sliced avocado and sprinkle with fresh parsley for garnish.
+8. Serve immediately or store in the fridge for a quick meal later.
+## Preparation Steps
+The process of preparing the Simple Chicken Bowl is straightforward, making it accessible even for those new to cooking. The first step involves cooking the quinoa according to the package instructions. Each brand may have slightly different instructions regarding water ratio and cooking times; thus, it is crucial to follow these guidelines to achieve the best texture. It's recommended to rinse the quinoa under cold water before cooking to remove its natural coating, known as saponin, which can give it a bitter taste.
+Next, you'll want to focus on the chicken. Whether you choose to grill or pan-sear, the goal is to ensure that the chicken is cooked thoroughly while maintaining juiciness. Cooking the chicken until it's fully cooked might take around 6-8 minutes per side, depending on your method, but using a meat thermometer can help you achieve perfect doneness (165°F is the safe internal temperature for poultry). Once cooked, slice the chicken into strips to make it easier to incorporate into the bowl.
+Steaming the broccoli is a fantastic way to retain its nutrients while also achieving the ideal tenderness without making it mushy. Aim for about 4 to 5 minutes of steaming, just until it turns vibrant green but still has a slight crunch. Overcooking can lead to loss of nutrients and an unappealing texture.
+As you prepare the bowl, combine all the cooked ingredients in a large mixing bowl, starting with the cooled quinoa at the base. Follow with the sliced grilled chicken, tender broccoli, and halved cherry tomatoes. This layering is key as it ensures the flavors blend throughout the dish. The next step involves drizzling the olive oil and lemon juice over the mixture for that burst of freshness, followed by seasoning with salt and pepper for taste. Tossing everything gently but diligently ensures that each bite is infused with those added flavors.
+Finally, just before serving, top the colorful mixture with avocado slices, which not only add creaminess but also an aesthetically pleasing finish to your bowl. Garnishing with fresh parsley ties it all together, delivering a fragrant herbaceous touch that complements the warm ingredients beautifully. You can serve it immediately or refrigerate it for later, making it a perfect dish for meal prep.
+In Part 2, we will explore specific cooking techniques and delve deeper into the nutritional benefits of the included ingredients, providing further insight into making this recipe a staple for healthy dining.
+### How to Properly Toss Salad Ingredients for Even Distribution
+When preparing your Simple Chicken Bowl, the method of combining the ingredients plays a crucial role in ensuring that each bite is equally delicious. It’s important to toss your salad ingredients properly for even coat and distribution of flavors. Start by placing the softer ingredients, such as the cherry tomatoes and avocado, on top of the cooked quinoa and chicken. This prevents the softer ingredients from being crushed under the weight of the heavier items. 
+Begin by drizzling the olive oil and lemon juice evenly over the salad, allowing the dressing to flow into the quinoa. Use tongs or a large spoon to gently lift and mix the ingredients from the bottom to the top rather than stirring aggressively. This method preserves the integrity of the avocado slices and ensures the grilled chicken and steamed broccoli get well-coated in oil and seasoning. Tasting the mixture after tossing will help determine if additional salt, pepper, or more dressing is needed.
+## Health Benefits
+In-depth Look at the Overall Nutritional Profile of the Simple Chicken Bowl
+The Simple Chicken Bowl offers a plethora of health benefits, balancing protein, carbohydrates, and healthy fats. With approximately 450 calories per serving, it's both filling and supportive of weight loss efforts. Each of the primary ingredients contributes essential nutrients, making it a wholesome option for anyone looking to maintain or improve their diet.
+### When examining the nutritional content:
+- **Quinoa**: A complete protein, containing all nine essential amino acids, quinoa is also a rich source of fiber, which aids in digestion and helps maintain steady blood sugar levels. 
+- **Grilled Chicken Breast**: Packed with lean protein, chicken breast supports muscle repair and growth while keeping you satiated for longer.
+- **Broccoli**: This cruciferous vegetable contains vitamins C and K, fiber, and numerous antioxidants, making it a powerhouse for overall health and immunity.
+- **Avocado**: Packed with heart-healthy monounsaturated fats, avocados contribute to improved cholesterol levels and provide valuable vitamins and minerals, particularly potassium.
+- **Cherry tomatoes**: They are an excellent source of vitamins A and C, alongside lycopene, an antioxidant linked to numerous health benefits.
+### Study of How Each Ingredient Contributes to a Healthy Diet
+This bowl is not just a combination of ingredients but a thoughtfully designed meal that aligns with dietary preferences focused on health. The complex carbohydrates from quinoa provide energy, while the high fiber content in both quinoa and vegetables helps maintain good digestive health. The healthy fats from avocado promote satiety and aid in the absorption of fat-soluble vitamins.
+### Discussion on Low-Calorie Meals and Weight Management
+Incorporating low-calorie meals like the Simple Chicken Bowl into your weekly routine can be beneficial for those looking to lose weight or maintain a healthy lifestyle. This dish fulfills the need for a balanced meal without excess calories. When dieting, maintaining nutrient density over calories consumed is key, and this bowl accomplishes just that while being flavorful and satisfying.
+## Serving Suggestions
+### Ideas for Pairing the Chicken Bowl with Other Healthy Sides
+This versatile chicken bowl pairs wonderfully with a variety of healthy sides. Consider adding a fresh side salad made with greens like spinach or arugula dressed simply with balsamic vinegar. Alternatively, a serving of fresh fruit, such as sliced apples or berries, offers a refreshing contrast to the savory elements of the chicken bowl.
+### Portion Control Tips for Meal Planning
+For those focusing on portion control, consider using smaller bowls or pre-measuring ingredients to avoid overeating. Each serving of the Simple Chicken Bowl is designed for one person, but if preparing meals for the week, scale up ingredients while keeping similar ratios, ensuring consistency across servings.
+### Variations and Customizations to Suit Taste Preferences
+The Simple Chicken Bowl is adaptable to suit various taste preferences. If you're looking to switch up flavors, add nuts for crunch or swap the protein for grilled shrimp or tofu. Adding spices like cumin or chili powder can elevate the flavor profile to suit different cuisines.
+## Meal Prep Tips
+### Steps for Preparing Ahead of Time for Busy Lifestyles
+To streamline meal preparation, start by cooking larger batches of quinoa and grilling extra chicken. These items can serve as a base for multiple meals throughout the week. Store each component separately in airtight containers in the fridge to maintain texture and quality.
+### Storage Recommendations: How Long the Dish Lasts in the Fridge
+When stored properly, the Simple Chicken Bowl components will last in the fridge for 3-4 days. Keep the assembled salad separate from the avocado to prevent browning and maintain freshness.
+### Reheating Instructions to Retain Freshness and Flavor
+When ready to enjoy, reheat the quinoa and chicken gently in the microwave or on the stovetop. Avoid reheating the avocado and the salad ingredients to ensure they retain their unique textures and flavors. Toss in fresh herbs after reheating for added freshness.
+## Dietary Considerations
+### Analysis of Common Dietary Needs Catered to by the Recipe
+This dish caters to various dietary preferences, making it an inclusive option. The use of quinoa, which is gluten-free, meets the needs of individuals with gluten sensitivities or celiac disease, while the lean protein content makes it suitable for those looking to maintain muscle mass.
+### Gluten-free: Quinoa as an Excellent Substitute
+Quinoa's gluten-free nature appeals to those with specific dietary restrictions. It serves as an excellent grain alternative in many dishes, enhancing nutritional value while offering a familiar texture.
+### Low-carb Alternatives for Those on a Keto Diet
+For those on a low-carb or ketogenic diet, consider reducing the amount of quinoa and increasing non-starchy vegetables like zucchini or bell peppers. This modification maintains a satisfying meal while lowering carbohydrate content. 
+### Vegan Adaptations: Substituting Chicken with Plant-Based Proteins
+To cater to vegan preferences, simply swap the grilled chicken for plant-based proteins such as chickpeas, tempeh, or even marinated tofu. These alternatives can provide a satisfactory texture and enough protein to keep you feeling full.
+## Flavor Enhancements
+### Suggestions for Adding Spices and Herbs for More Complex Flavors
+To elevate the taste of your Simple Chicken Bowl, consider adding spices such as paprika, garlic powder, or even a hint of cayenne for some heat. Fresh herbs like cilantro or basil can introduce aromatic layers to the dish.
+### Ingredients to Consider for Enhancing Taste Without Adding Calories
+Incorporating lemon zest or a splash of apple cider vinegar can enhance flavor significantly without adding calories. Fresh garlic, when sautéed lightly in olive oil, can also deepen the flavor profile.
+### The Role of Garnishes in Presentation and Taste
+Garnishes like parsley not only add visual appeal but also enhance flavor. A sprinkle of sesame seeds or a dash of chili flakes can add an extra crunch or kick, making the dish more exciting.
+## Environmental Impact
+### Discussion on the Sustainability of Ingredients Used
+In considering the environmental impact, the Simple Chicken Bowl leverages ingredients that can be sourced sustainably. Quinoa, being a crop that thrives in diverse climates, can be cultivated with reduced environmental strain when compared to conventionally farmed grains.
+### Benefits of Plant-Based Meals for the Environment
+Incorporating plant-based ingredients, such as quinoa and vegetables, contributes positively to eco-friendly eating habits. Shifting toward more plant-based meals can help reduce carbon footprints and resource consumption associated with animal farming.
+### Importance of Sourcing Local and Organic Products Where Possible
+Using local and organic products contributes to sustainability by reducing transportation emissions and supporting local economies. Opting for organic avocados and seasonal vegetables ensures that pesticides are kept to a minimum and contributes to preserving biodiversity.
+## Conclusion
+The Simple Chicken Bowl for Weight Loss is a wholesome dish that combines rich flavors with nutritious ingredients. It offers a balance of proteins, healthy fats, and vegetables that can be prepared in just 25 minutes, making it a practical choice for meals during a busy week. This bowl not only delights the palate but also supports a healthy lifestyle.
+</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simple Chicken Bowl for Weight Loss</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Quinoa Bowl Recipe for Weight Loss</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Quinoa Bowl Delight</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Enjoy a flavorful and nutritious chicken quinoa bowl that's perfect for weight loss and makes a healthy dinner option. This easy recipe features grilled chicken, fresh vegetables, and protein-packed quinoa, creating a satisfying meal that your family will love. Embrace a wholesome lifestyle with this delicious and nourishing bowl that keeps you on track with your wellness goals.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>chicken bowl, quinoa recipe, weight loss meal, healthy dinner, grilled chicken, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Chicken Bowl for Weight Loss</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Enjoy a nutritious Simple Chicken Bowl for weight loss, packed with quinoa, grilled chicken, and fresh veggies!</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_7.jpg</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2099,6 +3334,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523161/3c364b1180f.png</t>
@@ -2129,6 +3365,173 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Creamy High Protein Chicken Skillet Recipe
+## Introduction
+In the realm of weeknight dinners, creamy high protein chicken skillet dishes stand out for their simplicity, flavor, and nutritional benefits. This recipe showcases tender, juicy chicken combined with vibrant vegetables, enriched with Greek yogurt and Parmesan cheese, making it a wholesome meal option. Perfect for busy families or individuals seeking a hearty and nutritious entrée, this dish is both satisfying and quick to prepare.
+The stars of this dish are the succulent chicken breasts that absorb the delicious flavors from the seasoning and broth, creating a rich, creamy sauce. The addition of spinach not only contributes a vibrant green color but also infuses the meal with essential vitamins and minerals, while the cherry tomatoes add a burst of sweetness and juiciness. This well-rounded chicken skillet is ideal for busy weeknights or leisurely weekends when you want a meal that packs a punch in taste and nutrition.
+Notably, the use of Greek yogurt in this recipe introduces a velvety texture that one could often associate with cream-based dishes, but with added protein and lower fat content. It's a fantastic option for anyone looking to elevate their mealtime without a lot of fuss. With this easy-to-follow recipe, you can create a delightful dish that is bound to impress family and friends alike.
+## Recipe Overview
+- Prep Time: 10 minutes  
+- Cook Time: 15 minutes  
+- Total Time: 25 minutes  
+- Course: Main Course  
+- Cuisine: American  
+- Servings: 4  
+- Calories: ~350 per serving  
+## Ingredients
+- 1 lb boneless, skinless chicken breast, cut into bite-sized pieces
+- 1 cup Greek yogurt
+- 1 cup spinach, chopped
+- 1 cup cherry tomatoes, halved
+- 1/2 cup low-sodium chicken broth
+- 2 cloves garlic, minced
+- 1 tablespoon olive oil
+- 1 teaspoon Italian seasoning
+- Salt and pepper to taste
+- 1/4 cup grated Parmesan cheese
+### Discussion of Ingredient Quality and Selection
+Choosing high-quality ingredients makes a significant difference in the outcome of this creamy high protein chicken skillet. When selecting boneless, skinless chicken breasts, look for pieces that are fresh with a pink hue and minimal bruising. Frozen chicken may also work, but ensure it is thawed completely before cooking to achieve the best result.
+The use of low-sodium chicken broth is crucial not only for flavor but also for controlling the overall sodium content of the dish. This is essential for those monitoring salt intake while still wanting to enjoy a flavorful meal. Additionally, opting for fresh produce, such as spinach and cherry tomatoes, elevates the dish by providing vibrant flavors and nutrients. Fresh spinach offers a delicate earthy taste and packs a punch with vitamins like A and K, while cherry tomatoes contribute their natural sweetness.
+### Optional Ingredients and Variations
+Though this recipe is wonderfully complete as is, there is plenty of room to introduce personal touches. For instance, if you desire to incorporate more vegetables, consider peas, bell peppers, or mushrooms for added flavor and nutrition. These additions can complement the existing ingredients and enhance the dish's visual appeal.
+For those who may not have Greek yogurt on hand or prefer a non-dairy option, alternatives such as coconut yogurt or cashew cream can be utilized. Keep in mind that these substitutes might change the flavor profile slightly, but they can still create a creamy texture.
+{{image_ing_1}}
+## Preparation Steps
+Preparation is key to executing the creamy high protein chicken skillet with flair. Here’s a detailed guide on how to prepare each ingredient before cooking:
+- **Cutting the Chicken:** Begin by cutting the boneless, skinless chicken breast into bite-sized pieces. This will ensure even cooking and make it easier to incorporate into the creamy saucy blend later on.
+- **Halving the Cherry Tomatoes:** Next, halving the cherry tomatoes allows them to soften and release their juices during the cooking process. This not only adds a lovely sweetness to the dish but also creates a colorful presentation.
+- **Chopping the Spinach:** Fresh spinach should be roughly chopped to help it cook down quickly and evenly. This preparation step will allow it to blend beautifully with the other ingredients.
+### Importance of Having a Clean and Organized Workspace
+Before you begin cooking, having a clean and organized workspace is vital. This can enhance your cooking experience and ensure that you have all necessary tools at your disposal. Prepping all ingredients ahead of time (a method known as "mise en place") can help you streamline the cooking process efficiently. 
+Keep your cooking tools ready, including the skillet, spatula, and measuring cups—all within reach. This will help you focus on the task at hand, making it easier to enjoy the cooking process without any interruptions.
+## Cooking Instructions
+1. Heat olive oil in a large skillet over medium heat. This initial step is crucial as it prepares a rich base for your chicken to sear.
+2. Add the chicken pieces to the skillet, season with salt, pepper, and Italian seasoning, and cook until browned, about 5-7 minutes. Make sure to stir occasionally to ensure even browning on all sides. The chicken should be no longer pink inside when done.
+3. Stir in the minced garlic and cook for an additional 1-2 minutes until fragrant. The aroma of cooking garlic will indicate you are on the right path to creating a delightful flavor.
+4. Pour in the chicken broth and bring to a simmer. This step adds moisture and flavor to the mixture, helping the chicken to become tender and infusing the dish with layered flavors.
+5. Add the chopped spinach and cherry tomatoes, cooking until the spinach is wilted and tomatoes are softened, about 3-4 minutes. During this time, the colors will brighten, enhancing the dish's visual appeal.
+6. Lower the heat and stir in the Greek yogurt, mixing until well combined and creamy. This integration is key to achieving that luscious texture.
+7. Sprinkle the grated Parmesan cheese on top and stir until melted and incorporated. As the cheese melts, it enriches the sauce further, creating a satisfying creaminess.
+8. Allow the dish to warm through for another 2-3 minutes, adjusting seasoning if necessary. Tasting at this stage is essential to ensure perfect seasoning.
+9. Serve hot, garnished with extra Parmesan if desired. This final touch not only adds flavor but also aesthetic appeal to your delectable creation. 
+Stay tuned for Part 2, where we will delve into additional tips and tricks for perfecting this dish!
+## Modifying Cooking Time for Thicker Chicken Pieces
+When preparing the creamy high protein chicken skillet, it’s essential to consider the size of the chicken pieces. If you opt for thicker, bite-sized pieces, be prepared to adjust your cooking time. Thick chicken pieces may require additional cooking, resulting in a longer simmer to ensure the meat is cooked through. Typically, you can increase the initial cooking time for the chicken by an additional 2-3 minutes, checking the internal temperature to ensure it reaches 165°F (75°C) for safety. By making these adjustments, you guarantee that each piece is tender and flavorful while avoiding any undercooked centers.
+## Flavor Profile
+### Explanation of the Creamy and Savory Aspects of the Dish
+The overall flavor profile of the creamy high protein chicken skillet is a delightful combination of savory, creamy, and fresh elements. The creamy texture comes primarily from the Greek yogurt, which not only adds richness but also balances the savory notes from the chicken and Italian seasoning. This dish is designed to tantalize your taste buds, highlighting the unique flavors of its wholesome ingredients.
+### How the Greek Yogurt Lends Creaminess Without Excess Fat
+Greek yogurt serves as the cornerstone in creating the creamy texture of this dish while being significantly lower in fat compared to traditional cream. By utilizing one cup of Greek yogurt, you introduce a velvety richness that pairs perfectly with the dish's other ingredients. Additionally, Greek yogurt is a fantastic source of protein, elevating the nutritional value without compromising on taste.
+### The Role of Italian Seasoning in Enhancing Flavor
+Italian seasoning provides an aromatic complexity to the skillet meal, bringing in subtle herbaceous flavors that evoke the essence of Italian cuisine. A mixture that typically includes basil, oregano, rosemary, thyme, and sometimes sage or marjoram, it perfectly complements the chicken and creates a harmonious blend with the Greek yogurt and vegetables. This unique seasoning mix can transform an ordinary dish into an extraordinary culinary experience.
+### Balancing Flavors with Salt and Pepper
+Achieving the right balance of flavors is crucial in any recipe, and this chicken skillet is no exception. Salt enhances the natural flavors of the ingredients while pepper adds a hint of heat. As you cook, it’s important to taste the dish periodically. This practice allows you to adjust the salt and pepper levels to align with your personal preferences, ensuring that each mouthful is as delightful as the last.
+## Nutritional Benefits
+### Overview of the Health Benefits from Key Ingredients
+The creamy high protein chicken skillet is not only a feast for the senses but also a nutritional powerhouse. The primary protein source, boneless, skinless chicken breast, is packed with lean protein, essential for muscle repair and overall health. Coupled with Greek yogurt, this dish delivers a substantial protein content that supports a balanced diet.
+### Vitamins and Minerals from Spinach and Tomatoes
+Spinach and cherry tomatoes enrich this meal with an abundance of vitamins and minerals. Spinach is loaded with iron, calcium, and vitamin K, which are vital for bone health and blood production. Tomatoes provide a wealth of antioxidants, particularly lycopene, which is known for its health benefits, including improved heart health. Together, these vegetables contribute not only flavor but a medley of nutrients that play an essential role in overall wellness.
+### The Role of Fat and Calories in the Dish
+While this dish is designed to be healthier with the use of Greek yogurt and lean chicken, it's essential to consider the role of fat and calories. The creamy high protein chicken skillet clocking in at approximately 350 calories per serving is a reasonable option for a main course, but moderation is key even in a healthy meal. By being mindful of portion sizes, you can enjoy the richness without overindulging.
+## Serving Suggestions
+### Ideal Accompaniments for the Dish
+Pairing the creamy high protein chicken skillet with complementary side dishes can enhance the overall dining experience. Consider serving it alongside fluffy quinoa or hearty brown rice to absorb the delicious sauce and provide additional texture. A fresh green salad with a light vinaigrette can also balance the richness of the dish, adding a refreshing element to the meal.
+### Options for Meal Prep and Leftovers
+One of the great advantages of the creamy high protein chicken skillet is its suitability for meal prep. If you find yourself with leftovers, they can be conveniently stored in an airtight container in the refrigerator for up to three days. The flavors will continue to meld over time, making reheating just as delicious as when it was first made. 
+### Discussion About Serving Styles
+This dish can be served hot right from the skillet for a cozy family meal. Alternatively, if you prefer a more casual style, you can allow it to cool down and serve it as part of a buffet spread. The creamy chicken skillet can also be portioned into individual servings to store in the refrigerator for a quick, healthy lunch option throughout the week.
+## Storage and Reheating
+### Proper Storage Techniques to Maintain Freshness
+To keep your creamy high protein chicken skillet fresh, it's crucial to utilize proper storage techniques. Refrigerate leftovers in an airtight container to prevent moisture from entering, which can lead to spoilage. If you plan to enjoy it later, consider portioning it into smaller containers for easy access.
+### How to Freeze Individual Portions if Necessary
+For longer storage, freezing is an excellent option. Ensure that the dish has completely cooled before transferring it to freezer-safe containers. Individual portions allow for quick and easy reheating later, enabling a healthy meal option at a moment's notice. 
+### Step-by-Step Reheating Instructions
+For reheating, two popular methods include the microwave and stovetop. When using the microwave, place the portion in a microwave-safe dish, cover it loosely, and heat in 30-second intervals, stirring in between to ensure even warming. For stovetop reheating, transfer the chicken skillet to a pan over low heat, stirring occasionally and adding a splash of chicken broth or water if the sauce has thickened too much.
+## Common Mistakes to Avoid
+### Highlight Key Pitfalls When Preparing the Dish
+While preparing the creamy high protein chicken skillet, there are a few common pitfalls to be mindful of. Overcooking the chicken can lead to dryness, making the dish less enjoyable. Always ensure to check the chicken for doneness rather than relying solely on cooking time.
+### Not Adjusting Seasonings Based on Personal Taste
+Another prevalent mistake is not adjusting seasonings to suit your preferences. Everyone’s palate is different, and what might be perfect for one person may not be for another. Tasting throughout the cooking process ensures that the flavors are to your liking, allowing you to make necessary adjustments as you go.
+### Tips for Achieving a Creamy Consistency
+When incorporating Greek yogurt, timing is key. Adding it too early in the cooking process can result in curdling, especially if the skillet is too hot. To avoid this, lower the heat once all other ingredients are combined and then stir in the yogurt. This technique will deliver a beautifully creamy consistency without compromising the integrity of the yogurt.
+## Variations and Customizations
+### Suggestions for Ingredient Substitutions
+The creamy high protein chicken skillet can be easily customized to suit various dietary needs. If you're looking for alternative protein sources, turkey or even tofu can be great substitutes in this recipe, ensuring that everyone can enjoy the dish.
+### Alternative Cheese Options for Lactose-Intolerant Individuals
+For those who are lactose intolerant, consider using nutritional yeast instead of Parmesan cheese to provide a similar umami flavor without dairy. This substitution can make the dish accessible to a broader audience while maintaining its savory characteristics.
+### Seasonal Variations to Incorporate
+Incorporating seasonal vegetables can elevate the dish and make it more vibrant. During summer months, adding zucchini or bell peppers along with the spinach and tomatoes can introduce a variety of textures and flavors, making it even more delightful. Experimenting with seasonal produce not only enhances nutritional content but also keeps the recipe exciting and fresh.
+## Conclusion
+The creamy high protein chicken skillet embodies a delicious fusion of flavors and textures, making it an excellent main course for any weeknight meal. With a short preparation and cooking time, it allows for quick family dinners without sacrificing nutrition. The balance between protein, vegetables, and creamy elements ensures a satisfying and wholesome dish that is sure to please a variety of palates.
+</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Creamy High Protein Chicken Skillet Recipe</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Creamy High Protein Chicken Skillet Recipe with Spinach and Tomatoes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Creamy Spinach Chicken Delight</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>This creamy high protein chicken skillet recipe is the perfect easy dinner for busy weeknights. Packed with tender chicken, fresh spinach, and vibrant tomatoes, it gets a protein boost from Greek yogurt, creating a rich and satisfying meal. Enjoy the comforting flavors and vibrant colors that make this dish ideal for any season.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>creamy chicken, high protein, skillet recipe, Greek yogurt, spinach, easy dinner</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Creamy High Protein Chicken</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Enjoy a delicious and creamy high protein chicken skillet that's quick to make and packed with flavor! Perfect for dinner!</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_8.jpg</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2304,6 +3707,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523163/500f1a9d1d9.png</t>
@@ -2334,6 +3738,140 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Spicy Chicken Bowl High Protein Style
+## Introduction
+The Spicy Chicken Bowl High Protein Style is an exquisitely crafted dish that beautifully balances healthiness and flavor, making it an ideal main course. Perfect for those who wish to indulge in a satisfying yet nutritious meal, this recipe showcases vibrant colors and textures that delight the senses and tantalize the taste buds. The combination of protein-rich chicken, hearty quinoa, and a medley of colorful vegetables creates a captivating dish that excels in both presentation and taste.
+With an array of flavors that burst forth in each bite, this spicy chicken bowl is perfect for meal prep or a busy weeknight dinner. Whether you are serving it to family or friends, it is sure to impress with its heart-healthy ingredients and bold, spicy character. A garnish of fresh cilantro elevates the dish, offering a hint of freshness that beautifully contrasts with the warmth of the spices.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 20 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Mexican
+- Servings: 4
+- Calories: ~450 per serving
+## Ingredients
+- 1 lb boneless, skinless chicken breast, diced
+- 1 cup quinoa, rinsed
+- 1 can black beans, drained and rinsed
+- 1 cup corn, frozen or canned
+- 1 red bell pepper, diced
+- 1 avocado, sliced
+- 2 tablespoons olive oil
+- 2 tablespoons chili powder
+- 1 teaspoon cumin
+- Salt and pepper to taste
+- Fresh cilantro for garnish
+{{image_ing_1}}
+## Instructions
+1. In a medium saucepan, cook the quinoa according to package instructions; set aside.
+2. In a large skillet, heat the olive oil over medium heat and add the diced chicken.
+3. Season the chicken with chili powder, cumin, salt, and pepper. Cook until the chicken is browned and cooked through, about 6-8 minutes.
+4. Add the red bell pepper, black beans, and corn to the skillet; stir and cook for an additional 3-4 minutes until everything is heated through.
+5. Fluff the cooked quinoa with a fork and divide it among serving bowls.
+6. Top each bowl with the spicy chicken mixture and sliced avocado.
+7. Garnish with fresh cilantro before serving.
+## Cooking Techniques
+The preparation of the Spicy Chicken Bowl incorporates various cooking methods that enhance the ingredients' flavors and textures. Cooking quinoa is an essential step; it requires rinsing to eliminate bitterness from the outer coating known as saponin. Properly cooking quinoa results in a fluffy, light texture, which serves as the bed for the more robust flavors of the chicken and vegetables.
+Sautéing the chicken in olive oil over medium heat allows it to sear properly, which locks in juices and develops a golden-brown exterior. The seasoning with chili powder and cumin during cooking infuses the meat with robust flavors. It’s crucial not to overcrowd the skillet during this step, as that could prevent even cooking and browning.
+Moreover, combining the ingredients in the skillet allows for the melding of flavors. The heat develops from the cooked chicken is absorbed by the diced red bell peppers, black beans, and corn, creating a harmonious blend. Stirring the added ingredients ensures that they are evenly mixed, allowing for maximal flavor integration in every serving. The skillet technique effectively marries the spices with the protein and vegetables, making the entire dish vibrant and flavorful.
+## Nutritional Benefits
+The Spicy Chicken Bowl is not just a feast for the palate but also a powerhouse of nutritional benefits. The use of chicken breast comes with its advantages; it is an excellent source of high-quality protein with minimal fat content, making it a preferred choice for health-conscious individuals. This protein-rich meat helps in muscle building and recovery, vital for anyone maintaining an active lifestyle.
+Quinoa is another standout ingredient in this dish. Often hailed as a superfood, it is a complete protein source, meaning it provides all nine essential amino acids. Additionally, it is rich in fiber, aiding digestive health and helping to keep you full longer. This wholesome grain caters to various dietary needs, appealing to vegans and vegetarians alike when paired with complementary sources of protein.
+Black beans contribute an abundance of nutrients to the bowl. They are high in protein and fiber while also being a great source of vitamins and minerals. Their fiber content promotes digestive health and stabilizes blood sugar levels, making them a beneficial addition to this meal. Furthermore, the creamy slices of avocado provide heart-healthy fats and vitamin E, enhancing both the taste and nutrient profile of the dish.
+By combining these ingredients, the Spicy Chicken Bowl presents a well-rounded meal that nourishes the body while tantalizing the taste buds. Each portion boasts an impressive amount of protein, making it an ideal choice for anyone aiming to incorporate healthy eating into their lifestyle without sacrificing flavor. 
+The thoughtful selection of ingredients in the Spicy Chicken Bowl ensures that nutrition and taste walk hand in hand, making it a wholesome choice for lunch, dinner, or meal prep sessions.
+### Cilantro as a garnish: Bright flavors that elevate the dish
+Cilantro is not just a garnish but a key ingredient that adds a punch of freshness and vibrant flavor to the Spicy Chicken Bowl. Its unique aroma and slightly citrusy taste enhance the overall experience of the dish, balancing the richness of the chicken and creaminess of the avocado. When sprinkled generously over the completed bowl, fresh cilantro not only looks appealing but also offers a contrast to the bold spices that season the chicken. For those who enjoy a more herbaceous note, feel free to experiment with additional herbs, such as parsley or green onions, to tailor the dish to your liking. 
+## Meal Prep and Storage
+To make your weeknight meals more manageable, meal prepping the Spicy Chicken Bowl can be a game changer. You can cook the individual components in batches, allowing for easy assembly when you're ready to eat. Cooked quinoa, spicy chicken, black beans, and corn can be stored in airtight containers in the refrigerator for up to four days. This not only saves time during busy weeks but also helps reinforce a healthy diet with minimal effort.
+Best practices for refrigerating include letting the ingredients cool completely before sealing them in containers to prevent moisture buildup. When it's time to reheat, consider using the microwave for individual portions or an oven if you are warming multiple servings, as this can help retain moisture and prevent drying out.
+For long-term storage, you can freeze the chicken mixture and quinoa separately. Thaw them in the refrigerator the night before you plan to enjoy them, then reheat thoroughly before serving. This strategy also allows for customization; for example, you can triple or quadruple the recipe, making it versatile for different occasions or family meals throughout the month.
+## Pairing Suggestions
+When crafting the perfect meal, side dishes and beverages can enhance the Spicy Chicken Bowl experience. Fresh salads are a wonderful complement, particularly those with crisp greens like romaine or arugula, dressed in light vinaigrettes. Consider a cool cabbage slaw with a tangy lime dressing, as the crunchy texture and brightness will balance the bowl's warm components.
+For beverages, refreshing options, such as sparkling water with a splash of lime, or light beers like a Mexican Lager or Pilsner, can accentuate the vibrant flavors of the dish. If you prefer non-alcoholic choices, consider a chilled hibiscus iced tea that brings a fruity sweetness to the table.
+You can also elevate the Spicy Chicken Bowl with additional toppings to suit your palate. Crumbled feta cheese adds a creamy, salty element; diced jalapeños can bring additional heat, and tortilla strips provide a satisfying crunch that contrasts beautifully with other ingredients.
+## Serving Suggestions
+Presentation plays a crucial role in enhancing the dining experience, and the Spicy Chicken Bowl lends itself well to creative serving techniques. When layering your dish in a bowl, consider starting with quinoa at the bottom, followed by the spicy chicken mixture, and finally topped with avocado slices and cilantro. This not only looks appetizing but also promotes a delightful mix of textures and flavors in every bite.
+Choosing the right serving vessel matters too. Bowls are ideal for capturing all the ingredients in one scoop, but plates can also work if you want to spread out the components for a more visually appealing presentation. For a fun twist, consider wrapping the spicy chicken and toppings in large lettuce leaves or whole-grain tortillas. This creates an interactive, hands-on meal that's both light and satisfying.
+## Variations and Modifications
+The versatility of the Spicy Chicken Bowl allows it to cater to various dietary preferences and needs. For those adhering to a vegetarian lifestyle, swapping out the chicken for tofu or tempeh provides a robust source of protein without sacrificing flavor. Marinating the tofu or tempeh in the same spices used for the chicken can ensure that the dish remains just as flavorful.
+If you're sensitive to spice, consider reducing the amount of chili powder or trying a milder substitute, like smoked paprika. This helps maintain the flavor complexity without overwhelming your palate. Alternatively, if you're seeking to turn up the heat, adding fresh diced chilies or a dash of hot sauce can certainly spice things up.
+For those who are looking to switch up the grains, quinoa can be replaced with brown rice or farro, which offer varying textures and nutritional profiles. The choice of grain can transform the bowl while keeping the spirit of the dish intact.
+## Cooking Equipment
+Utilizing the correct cooking equipment makes preparing the Spicy Chicken Bowl efficient and enjoyable. A quality non-stick skillet is essential for browning the chicken without it sticking and making cleanup easier. A medium saucepan is necessary for cooking the quinoa perfectly, allowing for even absorption of water and flavor.
+In terms of utensils, a good chef’s knife for chopping vegetables and a reliable cutting board are indispensable. To conveniently rinse the quinoa and beans, a fine mesh strainer will ensure that excess starch and debris are removed without losing any ingredients. Having these tools on hand ensures a smooth cooking process, allowing you to focus on enjoying your time in the kitchen.
+## Conclusion
+The Spicy Chicken Bowl is a delightful combination of flavors and textures that come together in just 30 minutes, making it an ideal choice for nutritious weeknight dinners. The balance of spicy, savory, and fresh elements creates a satisfying meal, while the appealing presentation can make it a centerpiece for any gathering. Each serving is packed with protein and nutrition, ensuring everyone leaves the table feeling satisfied.
+</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Spicy Chicken Bowl High Protein Style</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Healthy Spicy Chicken Bowl with Quinoa and Avocado Recipe</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Spicy Chicken Quinoa Power Bowl</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Enjoy a delicious and nutritious Healthy Spicy Chicken Bowl that combines high protein chicken with wholesome quinoa and creamy avocado. This satisfying meal features black beans and vibrant Mexican cuisine flavors, making it perfect for any season. Elevate your dinner with this nourishing recipe that delivers on taste and health.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Spicy Chicken Bowl, High Protein, Quinoa, Black Beans, Avocado, Mexican Cuisine</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spicy Chicken Bowl</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Enjoy a delicious Spicy Chicken Bowl high in protein, perfect for a satisfying meal packed with flavor and nutrients!</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>dinner</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_9.jpg</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -3161,8 +3161,16 @@
           <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_7.jpg</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/simple-chicken-bowl-for-weight-loss/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3530,8 +3538,16 @@
           <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_8.jpg</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/creamy-high-protein-chicken-skillet-recipe/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3870,8 +3886,16 @@
           <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A1-Pinterest_01-out/output_images/image_9.jpg</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>https://easydessertsdaily.com/spicy-chicken-bowl-high-protein-style/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A1-Pinterest_01-out/Recipes.xlsx
+++ b/ALL/A1-Pinterest_01-out/Recipes.xlsx
@@ -76,10 +76,10 @@
     <t>error_ing</t>
   </si>
   <si>
+    <t>pinterest_title</t>
+  </si>
+  <si>
     <t>recipe_title_pin</t>
-  </si>
-  <si>
-    <t>pinterest_title</t>
   </si>
   <si>
     <t>pinterest_description</t>
@@ -1518,6 +1518,33 @@
     <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523163/1e1fdccc84a.png</t>
   </si>
   <si>
+    <t>Delicious High-Protein Chicken Bowl Recipe for Healthy Meal Prep</t>
+  </si>
+  <si>
+    <t>Quick and Easy 20-Minute High Protein Chicken and Quinoa Dinner Recipe</t>
+  </si>
+  <si>
+    <t>Delicious Healthy Chicken Bowl Recipe with Quinoa and Veggies for a Quick Dinner</t>
+  </si>
+  <si>
+    <t>Easy High Protein Chicken Meal Prep with Quinoa and Broccoli</t>
+  </si>
+  <si>
+    <t>Healthy Easy Chicken and Rice Recipe for High Protein Meals</t>
+  </si>
+  <si>
+    <t>Easy High Protein Chicken Wrap Recipe for Quick Lunches</t>
+  </si>
+  <si>
+    <t>Healthy Chicken Quinoa Bowl for Weight Loss: Quick &amp; Easy Recipe</t>
+  </si>
+  <si>
+    <t>Creamy High Protein Chicken Skillet Recipe with Spinach and Tomatoes</t>
+  </si>
+  <si>
+    <t>High Protein Spicy Chicken Bowl with Quinoa, Avocado, and Black Beans</t>
+  </si>
+  <si>
     <t>Protein-Packed Chicken Quinoa Bowl</t>
   </si>
   <si>
@@ -1543,33 +1570,6 @@
   </si>
   <si>
     <t>Spicy Chicken Quinoa Power Bowl</t>
-  </si>
-  <si>
-    <t>Delicious High-Protein Chicken Bowl Recipe for Healthy Meal Prep</t>
-  </si>
-  <si>
-    <t>Quick and Easy 20-Minute High Protein Chicken and Quinoa Dinner Recipe</t>
-  </si>
-  <si>
-    <t>Delicious Healthy Chicken Bowl Recipe with Quinoa and Veggies for a Quick Dinner</t>
-  </si>
-  <si>
-    <t>Easy High Protein Chicken Meal Prep with Quinoa and Broccoli</t>
-  </si>
-  <si>
-    <t>Healthy Easy Chicken and Rice Recipe for High Protein Meals</t>
-  </si>
-  <si>
-    <t>Easy High Protein Chicken Wrap Recipe for Quick Lunches</t>
-  </si>
-  <si>
-    <t>Healthy Chicken Quinoa Bowl for Weight Loss: Quick &amp; Easy Recipe</t>
-  </si>
-  <si>
-    <t>Creamy High Protein Chicken Skillet Recipe with Spinach and Tomatoes</t>
-  </si>
-  <si>
-    <t>High Protein Spicy Chicken Bowl with Quinoa, Avocado, and Black Beans</t>
   </si>
   <si>
     <t>Elevate your meal prep with this delicious high-protein chicken bowl recipe that features tender chicken, fluffy quinoa, and creamy avocado. Perfect for busy weekdays, this healthy recipe not only satisfies your hunger but also fuels your body with wholesome ingredients. Enjoy a nutritious and flavorful bowl that’s ideal for any meal of the day!</t>
